--- a/v4/창체_물품계획서_RPM.xlsx
+++ b/v4/창체_물품계획서_RPM.xlsx
@@ -109,7 +109,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -122,8 +122,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDDDDD"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -146,6 +151,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00808080"/>
+      </left>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
@@ -155,7 +174,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -220,7 +239,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -734,7 +756,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="24.9" customHeight="1" s="15">
+    <row r="5" ht="35" customHeight="1" s="15">
       <c r="A5" s="16" t="n">
         <v>3</v>
       </c>
@@ -804,7 +826,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="24.9" customHeight="1" s="15">
+    <row r="7" ht="35" customHeight="1" s="15">
       <c r="A7" s="16" t="n">
         <v>5</v>
       </c>
@@ -874,7 +896,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="24.9" customHeight="1" s="15">
+    <row r="9" ht="35" customHeight="1" s="15">
       <c r="A9" s="16" t="n">
         <v>7</v>
       </c>
@@ -944,7 +966,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="24.9" customHeight="1" s="15">
+    <row r="11" ht="35" customHeight="1" s="15">
       <c r="A11" s="16" t="n">
         <v>9</v>
       </c>
@@ -1010,7 +1032,7 @@
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6455358137</t>
+          <t>https://www.coupang.com/vp/products/6305734042</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1106,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="24.9" customHeight="1" s="15">
+    <row r="15" ht="35" customHeight="1" s="15">
       <c r="A15" s="16" t="n">
         <v>13</v>
       </c>
@@ -1119,7 +1141,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="24.9" customHeight="1" s="15">
+    <row r="16" ht="50" customHeight="1" s="15">
       <c r="A16" s="16" t="n">
         <v>14</v>
       </c>
@@ -1150,11 +1172,11 @@
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=%EC%98%A4%EC%BC%80%EC%9D%B4%EC%8A%A4%ED%94%84%EB%A7%81%20%EB%A7%9E%EC%B6%A4%20%EC%95%95%EC%B6%95%EC%8A%A4%ED%94%84%EB%A7%81</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="24.9" customHeight="1" s="15">
+          <t>https://www.coupang.com/np/search?q=오케이스프링 맞춤 압축스프링</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="50" customHeight="1" s="15">
       <c r="A17" s="16" t="n">
         <v>15</v>
       </c>
@@ -1185,7 +1207,7 @@
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=%EC%98%A4%EC%BC%80%EC%9D%B4%EC%8A%A4%ED%94%84%EB%A7%81%20%EB%A7%9E%EC%B6%A4%20%EC%95%95%EC%B6%95%EC%8A%A4%ED%94%84%EB%A7%81</t>
+          <t>https://www.coupang.com/np/search?q=오케이스프링 맞춤 압축스프링</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1522,7 @@
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6455358137</t>
+          <t>https://www.coupang.com/vp/products/7440529428</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1736,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="24.9" customHeight="1" s="15">
+    <row r="33" ht="35" customHeight="1" s="15">
       <c r="A33" s="16" t="n">
         <v>31</v>
       </c>
@@ -1889,7 +1911,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="24.9" customHeight="1" s="15">
+    <row r="38" ht="35" customHeight="1" s="15">
       <c r="A38" s="16" t="n">
         <v>36</v>
       </c>
@@ -1994,7 +2016,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="24.9" customHeight="1" s="15">
+    <row r="41" ht="35" customHeight="1" s="15">
       <c r="A41" s="16" t="n">
         <v>39</v>
       </c>
@@ -2414,7 +2436,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="24.9" customHeight="1" s="15">
+    <row r="53" ht="35" customHeight="1" s="15">
       <c r="A53" s="16" t="n">
         <v>51</v>
       </c>
@@ -2519,7 +2541,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="24.9" customHeight="1" s="15">
+    <row r="56" ht="35" customHeight="1" s="15">
       <c r="A56" s="16" t="n">
         <v>54</v>
       </c>
@@ -2550,7 +2572,7 @@
       </c>
       <c r="H56" s="12" t="inlineStr">
         <is>
-          <t>https://www.gmarket.co.kr/n/search?keyword=WH148%20B10K%20%ED%95%98%ED%94%84%20%EC%83%A4%ED%94%84%ED%8A%B8%2015mm</t>
+          <t>https://www.gmarket.co.kr/n/search?keyword=WH148 B10K 하프 샤프트 15mm</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2681,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="24.9" customHeight="1" s="15">
+    <row r="60" ht="35" customHeight="1" s="15">
       <c r="A60" s="16" t="n">
         <v>58</v>
       </c>
@@ -2694,7 +2716,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="24.9" customHeight="1" s="15">
+    <row r="61" ht="35" customHeight="1" s="15">
       <c r="A61" s="16" t="n">
         <v>59</v>
       </c>
@@ -2729,7 +2751,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="24.9" customHeight="1" s="15">
+    <row r="62" ht="35" customHeight="1" s="15">
       <c r="A62" s="16" t="n">
         <v>60</v>
       </c>
@@ -2764,7 +2786,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="24.9" customHeight="1" s="15">
+    <row r="63" ht="35" customHeight="1" s="15">
       <c r="A63" s="16" t="n">
         <v>61</v>
       </c>
@@ -2869,7 +2891,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="24.9" customHeight="1" s="15">
+    <row r="66" ht="35" customHeight="1" s="15">
       <c r="A66" s="16" t="n">
         <v>64</v>
       </c>
@@ -2939,7 +2961,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="24.9" customHeight="1" s="15">
+    <row r="68" ht="35" customHeight="1" s="15">
       <c r="A68" s="16" t="n">
         <v>66</v>
       </c>
@@ -3133,7 +3155,7 @@
     <col width="24" customWidth="1" style="15" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20" customHeight="1" s="15">
       <c r="A1" s="22" t="inlineStr">
         <is>
           <t>no</t>
@@ -3175,2391 +3197,2391 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="21" t="inlineStr">
+    <row r="2" ht="50" customHeight="1" s="15">
+      <c r="A2" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>볼 베어링 6001ZZ NSK</t>
         </is>
       </c>
-      <c r="C2" s="21" t="inlineStr">
+      <c r="C2" s="23" t="inlineStr">
         <is>
           <t>12×28×8</t>
         </is>
       </c>
-      <c r="D2" s="21" t="n">
+      <c r="D2" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="E2" s="21" t="inlineStr">
+      <c r="E2" s="23" t="inlineStr">
         <is>
           <t>끝판 4 · 출력 기어 12 · 아이들러 2 · 클러치 파일럿 1 = 19 + 여분 2</t>
         </is>
       </c>
-      <c r="F2" s="21" t="inlineStr">
+      <c r="F2" s="23" t="inlineStr">
         <is>
           <t>쿠팡 무명 10개 묶음 → NSK: 바깥지름 공차가 고르게 작아서 쿠폰으로 정한 압입 구멍이 21개 모두 맞고 소리가 작음</t>
         </is>
       </c>
-      <c r="G2" s="21" t="inlineStr">
+      <c r="G2" s="23" t="inlineStr">
         <is>
           <t>옵션 "NSK 6001 ZZ", 12×28×8, ZZ(철판 실드)</t>
         </is>
       </c>
-      <c r="H2" s="21" t="inlineStr">
+      <c r="H2" s="23" t="inlineStr">
         <is>
           <t>검색 결과 2026-10-22 (화면 미확인)</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="21" t="n">
+    <row r="3" ht="35" customHeight="1" s="15">
+      <c r="A3" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="21" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>볼 베어링 6003ZZ NSK</t>
         </is>
       </c>
-      <c r="C3" s="21" t="inlineStr">
+      <c r="C3" s="23" t="inlineStr">
         <is>
           <t>17×35×10</t>
         </is>
       </c>
-      <c r="D3" s="21" t="n">
+      <c r="D3" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="21" t="inlineStr">
+      <c r="E3" s="23" t="inlineStr">
         <is>
           <t>클러치 릴리스 1 + 여분 1</t>
         </is>
       </c>
-      <c r="F3" s="21" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t>같은 이유로 NSK</t>
         </is>
       </c>
-      <c r="G3" s="21" t="inlineStr">
+      <c r="G3" s="23" t="inlineStr">
         <is>
           <t>옵션 "NSK 6003ZZ", 17×35×10</t>
         </is>
       </c>
-      <c r="H3" s="21" t="inlineStr">
+      <c r="H3" s="23" t="inlineStr">
         <is>
           <t>검색 결과 2026-10-22 (화면 미확인)</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="21" t="n">
+    <row r="4" ht="35" customHeight="1" s="15">
+      <c r="A4" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="21" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>연마봉 Ø12 S45C 1m</t>
         </is>
       </c>
-      <c r="C4" s="21" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>435·358·160 으로 절단</t>
         </is>
       </c>
-      <c r="D4" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="21" t="inlineStr">
+      <c r="D4" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t>입력축 435 · 출력축 358 (둘 다 양면 D컷) · 레버봉 160</t>
         </is>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t>smball 에서 사려던 소망트레이딩의 G마켓 상품</t>
         </is>
       </c>
-      <c r="G4" s="21" t="inlineStr">
+      <c r="G4" s="23" t="inlineStr">
         <is>
           <t>옵션 100cm, 주문 메모에 절단 길이 435·358·160</t>
         </is>
       </c>
-      <c r="H4" s="21" t="inlineStr">
+      <c r="H4" s="23" t="inlineStr">
         <is>
           <t>smball 1m 16,000 기준 (G마켓 옵션가 미확인)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="21" t="n">
+    <row r="5" ht="35" customHeight="1" s="15">
+      <c r="A5" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>연마봉 Ø12 S45C 10cm</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>55 로 절단</t>
         </is>
       </c>
-      <c r="D5" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="21" t="inlineStr">
+      <c r="D5" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>후진 아이들러 축</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>같은 판매자</t>
         </is>
       </c>
-      <c r="G5" s="21" t="inlineStr">
+      <c r="G5" s="23" t="inlineStr">
         <is>
           <t>옵션 "12파이-10cm", 메모에 55mm</t>
         </is>
       </c>
-      <c r="H5" s="21" t="inlineStr">
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t>검색 결과 2026-10-22 (화면 미확인)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="21" t="n">
+    <row r="6" ht="35" customHeight="1" s="15">
+      <c r="A6" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>축 양면 D컷 가공</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>입력축 435·출력축 358, 면 사이 10.0, 전체 길이</t>
         </is>
       </c>
-      <c r="D6" s="21" t="n">
+      <c r="D6" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>기어·허브를 축에 고정 (도면 v4/도면_D컷축.pdf)</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t>기성품 없음 → 소망트레이딩 가공 의뢰 (smball Q&amp;A 14번 답변 대기)</t>
         </is>
       </c>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="G6" s="23" t="inlineStr">
         <is>
           <t>도면 첨부, 길이 ±0.5, 열처리봉이 어려우면 비열처리 S45C 도 됨</t>
         </is>
       </c>
-      <c r="H6" s="21" t="inlineStr">
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t>추정 (견적·옵션 확인 후 확정)</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="21" t="n">
+    <row r="7" ht="50" customHeight="1" s="15">
+      <c r="A7" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>스텐 환봉 Ø6 1m</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>371mm 2개로 절단</t>
         </is>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>변속 레일 3 + 여분 1</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>소망 6파이는 G마켓에 없음 → 스텐 환봉 절단판매 (무른 재질이라 러그·칼라 나사 끝이 잘 물림)</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t>1m 3,000 + 절단 2번 500×2, 371mm 2개씩 (남는 258 버림)</t>
         </is>
       </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t>검색 결과 2026-10-22 (화면 미확인)</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="21" t="n">
+    <row r="8" ht="20" customHeight="1" s="15">
+      <c r="A8" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>강철 평행핀 Ø5×25</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>100개, 공차 0~+0.01</t>
         </is>
       </c>
-      <c r="D8" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="D8" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>도그 24 + 여분</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="G8" s="23" t="inlineStr">
         <is>
           <t>옵션 "M5 (+)공차 / 25mm × 100개"</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t>확인 2026-10-20</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="21" t="n">
+    <row r="9" ht="20" customHeight="1" s="15">
+      <c r="A9" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>강철 평행핀 Ø5×40</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>공차 0~+0.01</t>
         </is>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>스프로킷 커플링 6 + 여분 2</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>여분 2 추가</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="G9" s="23" t="inlineStr">
         <is>
           <t>5x40 낱개</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="H9" s="23" t="inlineStr">
         <is>
           <t>확인 2026-10-20</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="21" t="n">
+    <row r="10" ht="35" customHeight="1" s="15">
+      <c r="A10" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>NBR 고무 호스</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>안지름 5 × 바깥지름 10, 약 2m</t>
         </is>
       </c>
-      <c r="D10" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="D10" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>핀 쿠션 6mm × 24 (144mm)</t>
         </is>
       </c>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t>도착하면 바깥지름 재기 (21 슬리브 출력 전)</t>
         </is>
       </c>
-      <c r="H10" s="21" t="inlineStr">
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t>확인 2026-10-20</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="21" t="n">
+    <row r="11" ht="20" customHeight="1" s="15">
+      <c r="A11" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>큰 와셔 DIN9021 M16 스텐</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>17×50×3</t>
         </is>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>클러치 원판 1 + 여분 1</t>
         </is>
       </c>
-      <c r="F11" s="21" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="G11" s="23" t="inlineStr">
         <is>
           <t>옵션 "M16 × 50mm"</t>
         </is>
       </c>
-      <c r="H11" s="21" t="inlineStr">
+      <c r="H11" s="23" t="inlineStr">
         <is>
           <t>확인 2026-10-20</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="21" t="n">
+    <row r="12" ht="20" customHeight="1" s="15">
+      <c r="A12" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>코르크 시트</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>2mm, A4 2매</t>
         </is>
       </c>
-      <c r="D12" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="D12" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>클러치 마찰 링 2 (바깥 Ø50, 안 Ø26)</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr"/>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="G12" s="23" t="inlineStr"/>
+      <c r="H12" s="23" t="inlineStr">
         <is>
           <t>확인 2026-10-20</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="21" t="n">
+    <row r="13" ht="20" customHeight="1" s="15">
+      <c r="A13" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>강구</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>Ø6, 50개</t>
         </is>
       </c>
-      <c r="D13" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="D13" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>러그 디텐트 3</t>
         </is>
       </c>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G13" s="21" t="inlineStr"/>
-      <c r="H13" s="21" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr"/>
+      <c r="H13" s="23" t="inlineStr">
         <is>
           <t>v3 단가</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="21" t="n">
+    <row r="14" ht="35" customHeight="1" s="15">
+      <c r="A14" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>샤프트 칼라 Ø6</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>안 6.1 · 바깥 11 · 폭 6, 10개</t>
         </is>
       </c>
-      <c r="D14" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="D14" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>레일 카트리지 6 + 여분 4</t>
         </is>
       </c>
-      <c r="F14" s="21" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G14" s="21" t="inlineStr">
+      <c r="G14" s="23" t="inlineStr">
         <is>
           <t>옵션 "01 D11xd6.1xH6mm"</t>
         </is>
       </c>
-      <c r="H14" s="21" t="inlineStr">
+      <c r="H14" s="23" t="inlineStr">
         <is>
           <t>확인 2026-10-20</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="21" t="n">
+    <row r="15" ht="50" customHeight="1" s="15">
+      <c r="A15" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>압축 스프링 맞춤 제작 (C252 동등)</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>SUS304 선경 1.6 · 외경 18.0 · 자유장 32 · 총 7권(유효 5) · 양끝 연삭</t>
         </is>
       </c>
-      <c r="D15" s="21" t="n">
+      <c r="D15" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>포크 카트리지 3 · 클러치 3 · 레버 후진 잠금 1 · 페달 복귀 2 = 9 + 여분 3</t>
         </is>
       </c>
-      <c r="F15" s="21" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>디바이스마트 C252 대신 (허용 쇼핑몰에 같은 기성품 없음). 계산 k 2.56 N/mm = C252 2.555 와 같음 → 설계 그대로</t>
         </is>
       </c>
-      <c r="G15" s="21" t="inlineStr">
+      <c r="G15" s="23" t="inlineStr">
         <is>
           <t>규격 그대로 전달: k 2.56 N/mm ±10% (21.6mm 로 누르면 26.6N), 밀착 높이 11.2 이하</t>
         </is>
       </c>
-      <c r="H15" s="21" t="inlineStr">
+      <c r="H15" s="23" t="inlineStr">
         <is>
           <t>추정 (견적·옵션 확인 후 확정)</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="21" t="n">
+    <row r="16" ht="50" customHeight="1" s="15">
+      <c r="A16" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>압축 스프링 맞춤 제작 (C147 동등)</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>SUS304 선경 0.45 · 외경 5.0 · 자유장 10 · 총 9권(유효 7)</t>
         </is>
       </c>
-      <c r="D16" s="21" t="n">
+      <c r="D16" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="E16" s="21" t="inlineStr">
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>러그 디텐트 3 + 여분 3</t>
         </is>
       </c>
-      <c r="F16" s="21" t="inlineStr">
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t>디바이스마트 C147 대신. k 0.54 N/mm (C147 0.50), 5mm 로 눌러도 밀착(4.05) 안 됨</t>
         </is>
       </c>
-      <c r="G16" s="21" t="inlineStr">
+      <c r="G16" s="23" t="inlineStr">
         <is>
           <t>같은 판매자에게 위 스프링과 함께 주문</t>
         </is>
       </c>
-      <c r="H16" s="21" t="inlineStr">
+      <c r="H16" s="23" t="inlineStr">
         <is>
           <t>추정 (견적·옵션 확인 후 확정)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="21" t="n">
+    <row r="17" ht="35" customHeight="1" s="15">
+      <c r="A17" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>M3 렌치볼트</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>M3×8</t>
         </is>
       </c>
-      <c r="D17" s="21" t="n">
+      <c r="D17" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>포크 카트리지 뚜껑 6 · 디텐트 3 + 여분 2</t>
         </is>
       </c>
-      <c r="F17" s="21" t="inlineStr">
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>여분 추가</t>
         </is>
       </c>
-      <c r="G17" s="21" t="inlineStr">
+      <c r="G17" s="23" t="inlineStr">
         <is>
           <t>스텐 유두(둥근머리) 낱개</t>
         </is>
       </c>
-      <c r="H17" s="21" t="inlineStr">
+      <c r="H17" s="23" t="inlineStr">
         <is>
           <t>확인 2026-10-20</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="21" t="n">
+    <row r="18" ht="20" customHeight="1" s="15">
+      <c r="A18" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>M3 렌치볼트</t>
         </is>
       </c>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>M3×10</t>
         </is>
       </c>
-      <c r="D18" s="21" t="n">
+      <c r="D18" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>클러치 포크 속선 누름 1 + 여분 1</t>
         </is>
       </c>
-      <c r="F18" s="21" t="inlineStr">
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t>여분 추가</t>
         </is>
       </c>
-      <c r="G18" s="21" t="inlineStr"/>
-      <c r="H18" s="21" t="inlineStr">
+      <c r="G18" s="23" t="inlineStr"/>
+      <c r="H18" s="23" t="inlineStr">
         <is>
           <t>확인 2026-10-20</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="21" t="n">
+    <row r="19" ht="50" customHeight="1" s="15">
+      <c r="A19" s="23" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>M3 렌치볼트</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>M3×12</t>
         </is>
       </c>
-      <c r="D19" s="21" t="n">
+      <c r="D19" s="23" t="n">
         <v>40</v>
       </c>
-      <c r="E19" s="21" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>칼라 7 · 클러치 덮개 7 · 축 끝 덮개 4 · 바퀴 덮개 2 · 아크릴 14 = 34 + 여분 6</t>
         </is>
       </c>
-      <c r="F19" s="21" t="inlineStr">
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>여분 추가</t>
         </is>
       </c>
-      <c r="G19" s="21" t="inlineStr"/>
-      <c r="H19" s="21" t="inlineStr">
+      <c r="G19" s="23" t="inlineStr"/>
+      <c r="H19" s="23" t="inlineStr">
         <is>
           <t>확인 2026-10-20</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="21" t="n">
+    <row r="20" ht="20" customHeight="1" s="15">
+      <c r="A20" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>M3 렌치볼트</t>
         </is>
       </c>
-      <c r="C20" s="21" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>M3×16</t>
         </is>
       </c>
-      <c r="D20" s="21" t="n">
+      <c r="D20" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E20" s="21" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>바퀴 덮개 받침 2 + 여분 1</t>
         </is>
       </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>여분 추가</t>
         </is>
       </c>
-      <c r="G20" s="21" t="inlineStr"/>
-      <c r="H20" s="21" t="inlineStr">
+      <c r="G20" s="23" t="inlineStr"/>
+      <c r="H20" s="23" t="inlineStr">
         <is>
           <t>확인 2026-10-20</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="21" t="n">
+    <row r="21" ht="20" customHeight="1" s="15">
+      <c r="A21" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>M3 렌치볼트 + 육각너트</t>
         </is>
       </c>
-      <c r="C21" s="21" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>M3×20</t>
         </is>
       </c>
-      <c r="D21" s="21" t="n">
+      <c r="D21" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>슬리브 결합 9 + 여분 2</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="F21" s="23" t="inlineStr">
         <is>
           <t>여분 추가</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="G21" s="23" t="inlineStr">
         <is>
           <t>볼트 70 + 스텐 육각너트 M3 60</t>
         </is>
       </c>
-      <c r="H21" s="21" t="inlineStr">
+      <c r="H21" s="23" t="inlineStr">
         <is>
           <t>확인 2026-10-20</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="21" t="n">
+    <row r="22" ht="20" customHeight="1" s="15">
+      <c r="A22" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="21" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>M3 렌치볼트</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>M3×25</t>
         </is>
       </c>
-      <c r="D22" s="21" t="n">
+      <c r="D22" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="E22" s="21" t="inlineStr">
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>러그 6 + 여분 2</t>
         </is>
       </c>
-      <c r="F22" s="21" t="inlineStr">
+      <c r="F22" s="23" t="inlineStr">
         <is>
           <t>여분 추가</t>
         </is>
       </c>
-      <c r="G22" s="21" t="inlineStr">
+      <c r="G22" s="23" t="inlineStr">
         <is>
           <t>M3×30 안 됨 (머리가 캐리어에 닿음)</t>
         </is>
       </c>
-      <c r="H22" s="21" t="inlineStr">
+      <c r="H22" s="23" t="inlineStr">
         <is>
           <t>확인 2026-10-20</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="21" t="n">
+    <row r="23" ht="20" customHeight="1" s="15">
+      <c r="A23" s="23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>M3 렌치볼트</t>
         </is>
       </c>
-      <c r="C23" s="21" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>M3×50</t>
         </is>
       </c>
-      <c r="D23" s="21" t="n">
+      <c r="D23" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E23" s="21" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>끝 채움판 4 + 여분 1</t>
         </is>
       </c>
-      <c r="F23" s="21" t="inlineStr">
+      <c r="F23" s="23" t="inlineStr">
         <is>
           <t>여분 추가</t>
         </is>
       </c>
-      <c r="G23" s="21" t="inlineStr"/>
-      <c r="H23" s="21" t="inlineStr">
+      <c r="G23" s="23" t="inlineStr"/>
+      <c r="H23" s="23" t="inlineStr">
         <is>
           <t>확인 2026-10-20</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="21" t="n">
+    <row r="24" ht="20" customHeight="1" s="15">
+      <c r="A24" s="23" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>M3 무두볼트 (오목끝)</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>M3×8</t>
         </is>
       </c>
-      <c r="D24" s="21" t="n">
+      <c r="D24" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E24" s="21" t="inlineStr">
+      <c r="E24" s="23" t="inlineStr">
         <is>
           <t>표시 바퀴 고정 1 + 여분 2</t>
         </is>
       </c>
-      <c r="F24" s="21" t="inlineStr">
+      <c r="F24" s="23" t="inlineStr">
         <is>
           <t>여분 추가</t>
         </is>
       </c>
-      <c r="G24" s="21" t="inlineStr"/>
-      <c r="H24" s="21" t="inlineStr">
+      <c r="G24" s="23" t="inlineStr"/>
+      <c r="H24" s="23" t="inlineStr">
         <is>
           <t>확인 2026-10-20</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="21" t="n">
+    <row r="25" ht="35" customHeight="1" s="15">
+      <c r="A25" s="23" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>M3 평와셔 스텐</t>
         </is>
       </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>바깥 8 × 두께 0.5</t>
         </is>
       </c>
-      <c r="D25" s="21" t="n">
+      <c r="D25" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>아크릴 나사 밑 14 · 속선 누름 1 + 여분 5</t>
         </is>
       </c>
-      <c r="F25" s="21" t="inlineStr">
+      <c r="F25" s="23" t="inlineStr">
         <is>
           <t>여분 추가</t>
         </is>
       </c>
-      <c r="G25" s="21" t="inlineStr">
+      <c r="G25" s="23" t="inlineStr">
         <is>
           <t>"스텐 평와셔 M3x8x0.5T"</t>
         </is>
       </c>
-      <c r="H25" s="21" t="inlineStr">
+      <c r="H25" s="23" t="inlineStr">
         <is>
           <t>확인 2026-10-20</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="21" t="n">
+    <row r="26" ht="20" customHeight="1" s="15">
+      <c r="A26" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="21" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>M4 렌치볼트 + 너트</t>
         </is>
       </c>
-      <c r="C26" s="21" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>M4×16</t>
         </is>
       </c>
-      <c r="D26" s="21" t="n">
+      <c r="D26" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E26" s="21" t="inlineStr">
+      <c r="E26" s="23" t="inlineStr">
         <is>
           <t>클러치 포크 브래킷 4 + 여분 1</t>
         </is>
       </c>
-      <c r="F26" s="21" t="inlineStr">
+      <c r="F26" s="23" t="inlineStr">
         <is>
           <t>여분 추가</t>
         </is>
       </c>
-      <c r="G26" s="21" t="inlineStr"/>
-      <c r="H26" s="21" t="inlineStr">
+      <c r="G26" s="23" t="inlineStr"/>
+      <c r="H26" s="23" t="inlineStr">
         <is>
           <t>확인 2026-10-20</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="21" t="n">
+    <row r="27" ht="20" customHeight="1" s="15">
+      <c r="A27" s="23" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>M4 렌치볼트 + 너트</t>
         </is>
       </c>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="C27" s="23" t="inlineStr">
         <is>
           <t>M4×25</t>
         </is>
       </c>
-      <c r="D27" s="21" t="n">
+      <c r="D27" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>페달 발판 4 + 여분 1</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="F27" s="23" t="inlineStr">
         <is>
           <t>여분 추가</t>
         </is>
       </c>
-      <c r="G27" s="21" t="inlineStr"/>
-      <c r="H27" s="21" t="inlineStr">
+      <c r="G27" s="23" t="inlineStr"/>
+      <c r="H27" s="23" t="inlineStr">
         <is>
           <t>확인 2026-10-20</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="21" t="n">
+    <row r="28" ht="35" customHeight="1" s="15">
+      <c r="A28" s="23" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>M4 렌치볼트 + 너트</t>
         </is>
       </c>
-      <c r="C28" s="21" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>M4×30</t>
         </is>
       </c>
-      <c r="D28" s="21" t="n">
+      <c r="D28" s="23" t="n">
         <v>23</v>
       </c>
-      <c r="E28" s="21" t="inlineStr">
+      <c r="E28" s="23" t="inlineStr">
         <is>
           <t>케이지 4 · 피벗 8 · 게이트 4 · 받침 브래킷 4 = 20 + 여분 3</t>
         </is>
       </c>
-      <c r="F28" s="21" t="inlineStr">
+      <c r="F28" s="23" t="inlineStr">
         <is>
           <t>여분 추가</t>
         </is>
       </c>
-      <c r="G28" s="21" t="inlineStr"/>
-      <c r="H28" s="21" t="inlineStr">
+      <c r="G28" s="23" t="inlineStr"/>
+      <c r="H28" s="23" t="inlineStr">
         <is>
           <t>확인 2026-10-20</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="21" t="n">
+    <row r="29" ht="20" customHeight="1" s="15">
+      <c r="A29" s="23" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="21" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>M4 렌치볼트 + 너트</t>
         </is>
       </c>
-      <c r="C29" s="21" t="inlineStr">
+      <c r="C29" s="23" t="inlineStr">
         <is>
           <t>M4×60</t>
         </is>
       </c>
-      <c r="D29" s="21" t="n">
+      <c r="D29" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E29" s="21" t="inlineStr">
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>클러치 기둥 3 + 여분 1</t>
         </is>
       </c>
-      <c r="F29" s="21" t="inlineStr">
+      <c r="F29" s="23" t="inlineStr">
         <is>
           <t>여분 추가</t>
         </is>
       </c>
-      <c r="G29" s="21" t="inlineStr"/>
-      <c r="H29" s="21" t="inlineStr">
+      <c r="G29" s="23" t="inlineStr"/>
+      <c r="H29" s="23" t="inlineStr">
         <is>
           <t>확인 2026-10-20</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="21" t="n">
+    <row r="30" ht="20" customHeight="1" s="15">
+      <c r="A30" s="23" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="21" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>M5 렌치볼트 + 너트</t>
         </is>
       </c>
-      <c r="C30" s="21" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>M5×10</t>
         </is>
       </c>
-      <c r="D30" s="21" t="n">
+      <c r="D30" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E30" s="21" t="inlineStr">
+      <c r="E30" s="23" t="inlineStr">
         <is>
           <t>클러치 조절나사 3 + 여분 1</t>
         </is>
       </c>
-      <c r="F30" s="21" t="inlineStr">
+      <c r="F30" s="23" t="inlineStr">
         <is>
           <t>여분 추가</t>
         </is>
       </c>
-      <c r="G30" s="21" t="inlineStr">
+      <c r="G30" s="23" t="inlineStr">
         <is>
           <t>M5×12 이상 금지 (클러치 토크 초과)</t>
         </is>
       </c>
-      <c r="H30" s="21" t="inlineStr">
+      <c r="H30" s="23" t="inlineStr">
         <is>
           <t>확인 2026-10-20</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="21" t="n">
+    <row r="31" ht="20" customHeight="1" s="15">
+      <c r="A31" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="21" t="inlineStr">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>M5 렌치볼트 + 너트</t>
         </is>
       </c>
-      <c r="C31" s="21" t="inlineStr">
+      <c r="C31" s="23" t="inlineStr">
         <is>
           <t>M5×20</t>
         </is>
       </c>
-      <c r="D31" s="21" t="n">
+      <c r="D31" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E31" s="21" t="inlineStr">
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>클러치 릴리스 누름 3 + 여분 1</t>
         </is>
       </c>
-      <c r="F31" s="21" t="inlineStr">
+      <c r="F31" s="23" t="inlineStr">
         <is>
           <t>여분 추가</t>
         </is>
       </c>
-      <c r="G31" s="21" t="inlineStr"/>
-      <c r="H31" s="21" t="inlineStr">
+      <c r="G31" s="23" t="inlineStr"/>
+      <c r="H31" s="23" t="inlineStr">
         <is>
           <t>확인 2026-10-20</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="21" t="n">
+    <row r="32" ht="35" customHeight="1" s="15">
+      <c r="A32" s="23" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="21" t="inlineStr">
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>M5 조정용 볼트 세트</t>
         </is>
       </c>
-      <c r="C32" s="21" t="inlineStr">
+      <c r="C32" s="23" t="inlineStr">
         <is>
           <t>M5×8 3 + M5×12 3 + M5 평와셔 3</t>
         </is>
       </c>
-      <c r="D32" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="21" t="inlineStr">
+      <c r="D32" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="23" t="inlineStr">
         <is>
           <t>클러치 토크 시험 3 결과로 조절나사 바꿈</t>
         </is>
       </c>
-      <c r="F32" s="21" t="inlineStr">
+      <c r="F32" s="23" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G32" s="21" t="inlineStr"/>
-      <c r="H32" s="21" t="inlineStr">
+      <c r="G32" s="23" t="inlineStr"/>
+      <c r="H32" s="23" t="inlineStr">
         <is>
           <t>확인 2026-10-20</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="21" t="n">
+    <row r="33" ht="35" customHeight="1" s="15">
+      <c r="A33" s="23" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="21" t="inlineStr">
+      <c r="B33" s="23" t="inlineStr">
         <is>
           <t>M5 렌치볼트 + 나일론 너트</t>
         </is>
       </c>
-      <c r="C33" s="21" t="inlineStr">
+      <c r="C33" s="23" t="inlineStr">
         <is>
           <t>M5×70</t>
         </is>
       </c>
-      <c r="D33" s="21" t="n">
+      <c r="D33" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E33" s="21" t="inlineStr">
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t>클러치 포크 피벗 1 + 여분 1</t>
         </is>
       </c>
-      <c r="F33" s="21" t="inlineStr">
+      <c r="F33" s="23" t="inlineStr">
         <is>
           <t>여분 추가</t>
         </is>
       </c>
-      <c r="G33" s="21" t="inlineStr"/>
-      <c r="H33" s="21" t="inlineStr">
+      <c r="G33" s="23" t="inlineStr"/>
+      <c r="H33" s="23" t="inlineStr">
         <is>
           <t>확인 2026-10-20</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="21" t="n">
+    <row r="34" ht="20" customHeight="1" s="15">
+      <c r="A34" s="23" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="21" t="inlineStr">
+      <c r="B34" s="23" t="inlineStr">
         <is>
           <t>M6 렌치볼트</t>
         </is>
       </c>
-      <c r="C34" s="21" t="inlineStr">
+      <c r="C34" s="23" t="inlineStr">
         <is>
           <t>M6×25</t>
         </is>
       </c>
-      <c r="D34" s="21" t="n">
+      <c r="D34" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="E34" s="21" t="inlineStr">
+      <c r="E34" s="23" t="inlineStr">
         <is>
           <t>모터 받침 4 · 페달 피벗 2 + 여분 1</t>
         </is>
       </c>
-      <c r="F34" s="21" t="inlineStr">
+      <c r="F34" s="23" t="inlineStr">
         <is>
           <t>여분 추가</t>
         </is>
       </c>
-      <c r="G34" s="21" t="inlineStr">
+      <c r="G34" s="23" t="inlineStr">
         <is>
           <t>M6×30 이상 금지</t>
         </is>
       </c>
-      <c r="H34" s="21" t="inlineStr">
+      <c r="H34" s="23" t="inlineStr">
         <is>
           <t>확인 2026-10-20</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="21" t="n">
+    <row r="35" ht="20" customHeight="1" s="15">
+      <c r="A35" s="23" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="21" t="inlineStr">
+      <c r="B35" s="23" t="inlineStr">
         <is>
           <t>M6 너트</t>
         </is>
       </c>
-      <c r="C35" s="21" t="inlineStr">
+      <c r="C35" s="23" t="inlineStr">
         <is>
           <t>M6 (맞변 10)</t>
         </is>
       </c>
-      <c r="D35" s="21" t="n">
+      <c r="D35" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E35" s="21" t="inlineStr">
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t>모터 받침 4 + 여분 1</t>
         </is>
       </c>
-      <c r="F35" s="21" t="inlineStr">
+      <c r="F35" s="23" t="inlineStr">
         <is>
           <t>여분 추가</t>
         </is>
       </c>
-      <c r="G35" s="21" t="inlineStr"/>
-      <c r="H35" s="21" t="inlineStr">
+      <c r="G35" s="23" t="inlineStr"/>
+      <c r="H35" s="23" t="inlineStr">
         <is>
           <t>확인 2026-10-20</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="21" t="n">
+    <row r="36" ht="20" customHeight="1" s="15">
+      <c r="A36" s="23" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="21" t="inlineStr">
+      <c r="B36" s="23" t="inlineStr">
         <is>
           <t>M6 나일론 너트</t>
         </is>
       </c>
-      <c r="C36" s="21" t="inlineStr">
+      <c r="C36" s="23" t="inlineStr">
         <is>
           <t>M6 (DIN985)</t>
         </is>
       </c>
-      <c r="D36" s="21" t="n">
+      <c r="D36" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E36" s="21" t="inlineStr">
+      <c r="E36" s="23" t="inlineStr">
         <is>
           <t>페달 피벗 2 + 여분 1</t>
         </is>
       </c>
-      <c r="F36" s="21" t="inlineStr">
+      <c r="F36" s="23" t="inlineStr">
         <is>
           <t>여분 추가</t>
         </is>
       </c>
-      <c r="G36" s="21" t="inlineStr"/>
-      <c r="H36" s="21" t="inlineStr">
+      <c r="G36" s="23" t="inlineStr"/>
+      <c r="H36" s="23" t="inlineStr">
         <is>
           <t>확인 2026-10-20</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="21" t="n">
+    <row r="37" ht="35" customHeight="1" s="15">
+      <c r="A37" s="23" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="21" t="inlineStr">
+      <c r="B37" s="23" t="inlineStr">
         <is>
           <t>목재 나사 스텐 둥근머리</t>
         </is>
       </c>
-      <c r="C37" s="21" t="inlineStr">
+      <c r="C37" s="23" t="inlineStr">
         <is>
           <t>4×16, 26개 봉</t>
         </is>
       </c>
-      <c r="D37" s="21" t="n">
+      <c r="D37" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E37" s="21" t="inlineStr">
+      <c r="E37" s="23" t="inlineStr">
         <is>
           <t>받침 브래킷 8 · 클러치 덮개 4 · 모터 받침 4 · 페달 받침 8 = 24 + 여분</t>
         </is>
       </c>
-      <c r="F37" s="21" t="inlineStr">
+      <c r="F37" s="23" t="inlineStr">
         <is>
           <t>1봉 → 2봉</t>
         </is>
       </c>
-      <c r="G37" s="21" t="inlineStr">
+      <c r="G37" s="23" t="inlineStr">
         <is>
           <t>옵션 "e)4x16mm-26개", 4×20 이상 안 됨</t>
         </is>
       </c>
-      <c r="H37" s="21" t="inlineStr">
+      <c r="H37" s="23" t="inlineStr">
         <is>
           <t>확인 2026-10-20</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="21" t="n">
+    <row r="38" ht="35" customHeight="1" s="15">
+      <c r="A38" s="23" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="21" t="inlineStr">
+      <c r="B38" s="23" t="inlineStr">
         <is>
           <t>2액형 에폭시 접착제</t>
         </is>
       </c>
-      <c r="C38" s="21" t="inlineStr">
+      <c r="C38" s="23" t="inlineStr">
         <is>
           <t>주사기형 25ml</t>
         </is>
       </c>
-      <c r="D38" s="21" t="n">
+      <c r="D38" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E38" s="21" t="inlineStr">
+      <c r="E38" s="23" t="inlineStr">
         <is>
           <t>레버봉·아이들러 축·클러치 와셔·쿠션 24·가변저항</t>
         </is>
       </c>
-      <c r="F38" s="21" t="inlineStr">
+      <c r="F38" s="23" t="inlineStr">
         <is>
           <t>1 → 2 (쿠션 24개)</t>
         </is>
       </c>
-      <c r="G38" s="21" t="inlineStr"/>
-      <c r="H38" s="21" t="inlineStr">
+      <c r="G38" s="23" t="inlineStr"/>
+      <c r="H38" s="23" t="inlineStr">
         <is>
           <t>확인 2026-10-20</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="21" t="n">
+    <row r="39" ht="20" customHeight="1" s="15">
+      <c r="A39" s="23" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="21" t="inlineStr">
+      <c r="B39" s="23" t="inlineStr">
         <is>
           <t>순간접착제</t>
         </is>
       </c>
-      <c r="C39" s="21" t="inlineStr">
+      <c r="C39" s="23" t="inlineStr">
         <is>
           <t>젤 타입 2개</t>
         </is>
       </c>
-      <c r="D39" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="21" t="inlineStr">
+      <c r="D39" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="23" t="inlineStr">
         <is>
           <t>덮개 스위치·홀센서·자석</t>
         </is>
       </c>
-      <c r="F39" s="21" t="inlineStr">
+      <c r="F39" s="23" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G39" s="21" t="inlineStr"/>
-      <c r="H39" s="21" t="inlineStr">
+      <c r="G39" s="23" t="inlineStr"/>
+      <c r="H39" s="23" t="inlineStr">
         <is>
           <t>확인 2026-10-20</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="21" t="n">
+    <row r="40" ht="35" customHeight="1" s="15">
+      <c r="A40" s="23" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="21" t="inlineStr">
+      <c r="B40" s="23" t="inlineStr">
         <is>
           <t>자전거 브레이크 케이블 세트</t>
         </is>
       </c>
-      <c r="C40" s="21" t="inlineStr">
+      <c r="C40" s="23" t="inlineStr">
         <is>
           <t>속선 2 + 아우터 Ø5 + 끝 캡</t>
         </is>
       </c>
-      <c r="D40" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" s="21" t="inlineStr">
+      <c r="D40" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="23" t="inlineStr">
         <is>
           <t>클러치 페달 → 클러치 포크 (속선 1 여분)</t>
         </is>
       </c>
-      <c r="F40" s="21" t="inlineStr">
+      <c r="F40" s="23" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G40" s="21" t="inlineStr">
+      <c r="G40" s="23" t="inlineStr">
         <is>
           <t>아우터 바깥지름 5</t>
         </is>
       </c>
-      <c r="H40" s="21" t="inlineStr">
+      <c r="H40" s="23" t="inlineStr">
         <is>
           <t>확인 2026-10-20</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="21" t="n">
+    <row r="41" ht="20" customHeight="1" s="15">
+      <c r="A41" s="23" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="21" t="inlineStr">
+      <c r="B41" s="23" t="inlineStr">
         <is>
           <t>MDF 판</t>
         </is>
       </c>
-      <c r="C41" s="21" t="inlineStr">
+      <c r="C41" s="23" t="inlineStr">
         <is>
           <t>12T 300×1200 재단</t>
         </is>
       </c>
-      <c r="D41" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="21" t="inlineStr">
+      <c r="D41" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="23" t="inlineStr">
         <is>
           <t>바닥판 750×300 + 페달 받침판 450×300</t>
         </is>
       </c>
-      <c r="F41" s="21" t="inlineStr">
+      <c r="F41" s="23" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G41" s="21" t="inlineStr"/>
-      <c r="H41" s="21" t="inlineStr">
+      <c r="G41" s="23" t="inlineStr"/>
+      <c r="H41" s="23" t="inlineStr">
         <is>
           <t>v3 단가</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="21" t="n">
+    <row r="42" ht="35" customHeight="1" s="15">
+      <c r="A42" s="23" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="21" t="inlineStr">
+      <c r="B42" s="23" t="inlineStr">
         <is>
           <t>투명 아크릴 3T 치수 재단</t>
         </is>
       </c>
-      <c r="C42" s="21" t="inlineStr">
+      <c r="C42" s="23" t="inlineStr">
         <is>
           <t>250×321</t>
         </is>
       </c>
-      <c r="D42" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" s="21" t="inlineStr">
+      <c r="D42" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="23" t="inlineStr">
         <is>
           <t>덮개 윗판</t>
         </is>
       </c>
-      <c r="F42" s="21" t="inlineStr">
+      <c r="F42" s="23" t="inlineStr">
         <is>
           <t>A3 원판을 손으로 자르는 대신 치수 재단 (모서리 곧음)</t>
         </is>
       </c>
-      <c r="G42" s="21" t="inlineStr">
+      <c r="G42" s="23" t="inlineStr">
         <is>
           <t>옵션에 크기 입력, 구멍은 직접 Ø3.4 (설계서 5장 위치)</t>
         </is>
       </c>
-      <c r="H42" s="21" t="inlineStr">
+      <c r="H42" s="23" t="inlineStr">
         <is>
           <t>추정 (견적·옵션 확인 후 확정)</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="21" t="n">
+    <row r="43" ht="35" customHeight="1" s="15">
+      <c r="A43" s="23" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="21" t="inlineStr">
+      <c r="B43" s="23" t="inlineStr">
         <is>
           <t>투명 아크릴 3T 치수 재단</t>
         </is>
       </c>
-      <c r="C43" s="21" t="inlineStr">
+      <c r="C43" s="23" t="inlineStr">
         <is>
           <t>200×321</t>
         </is>
       </c>
-      <c r="D43" s="21" t="n">
+      <c r="D43" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E43" s="21" t="inlineStr">
+      <c r="E43" s="23" t="inlineStr">
         <is>
           <t>덮개 옆판 2</t>
         </is>
       </c>
-      <c r="F43" s="21" t="inlineStr">
+      <c r="F43" s="23" t="inlineStr">
         <is>
           <t>같음</t>
         </is>
       </c>
-      <c r="G43" s="21" t="inlineStr">
+      <c r="G43" s="23" t="inlineStr">
         <is>
           <t>같음</t>
         </is>
       </c>
-      <c r="H43" s="21" t="inlineStr">
+      <c r="H43" s="23" t="inlineStr">
         <is>
           <t>추정 (견적·옵션 확인 후 확정)</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="21" t="n">
+    <row r="44" ht="20" customHeight="1" s="15">
+      <c r="A44" s="23" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="21" t="inlineStr">
+      <c r="B44" s="23" t="inlineStr">
         <is>
           <t>투명 아크릴 A3 3T (여분)</t>
         </is>
       </c>
-      <c r="C44" s="21" t="inlineStr">
+      <c r="C44" s="23" t="inlineStr">
         <is>
           <t>297×420</t>
         </is>
       </c>
-      <c r="D44" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" s="21" t="inlineStr">
+      <c r="D44" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="23" t="inlineStr">
         <is>
           <t>구멍 뚫다 깨질 때 바로 다시 자름</t>
         </is>
       </c>
-      <c r="F44" s="21" t="inlineStr">
+      <c r="F44" s="23" t="inlineStr">
         <is>
           <t>새로 추가</t>
         </is>
       </c>
-      <c r="G44" s="21" t="inlineStr"/>
-      <c r="H44" s="21" t="inlineStr">
+      <c r="G44" s="23" t="inlineStr"/>
+      <c r="H44" s="23" t="inlineStr">
         <is>
           <t>v3 단가</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="21" t="n">
+    <row r="45" ht="35" customHeight="1" s="15">
+      <c r="A45" s="23" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="21" t="inlineStr">
+      <c r="B45" s="23" t="inlineStr">
         <is>
           <t>PTFE 합성 그리스 (슈퍼루브)</t>
         </is>
       </c>
-      <c r="C45" s="21" t="inlineStr">
+      <c r="C45" s="23" t="inlineStr">
         <is>
           <t>85g</t>
         </is>
       </c>
-      <c r="D45" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" s="21" t="inlineStr">
+      <c r="D45" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="23" t="inlineStr">
         <is>
           <t>기어 이·슬리브 키·레일</t>
         </is>
       </c>
-      <c r="F45" s="21" t="inlineStr">
+      <c r="F45" s="23" t="inlineStr">
         <is>
           <t>새로 추가: 플라스틱에 써도 되는 그리스 → 마모·소음 줄임</t>
         </is>
       </c>
-      <c r="G45" s="21" t="inlineStr">
+      <c r="G45" s="23" t="inlineStr">
         <is>
           <t>PTFE(테프론) 합성 그리스</t>
         </is>
       </c>
-      <c r="H45" s="21" t="inlineStr">
+      <c r="H45" s="23" t="inlineStr">
         <is>
           <t>추정 (견적·옵션 확인 후 확정)</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="21" t="n">
+    <row r="46" ht="35" customHeight="1" s="15">
+      <c r="A46" s="23" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="21" t="inlineStr">
+      <c r="B46" s="23" t="inlineStr">
         <is>
           <t>나사 고정제 록타이트 243</t>
         </is>
       </c>
-      <c r="C46" s="21" t="inlineStr">
+      <c r="C46" s="23" t="inlineStr">
         <is>
           <t>10ml</t>
         </is>
       </c>
-      <c r="D46" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" s="21" t="inlineStr">
+      <c r="D46" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="23" t="inlineStr">
         <is>
           <t>금속끼리 나사: 칼라 무두볼트, 모터 M6</t>
         </is>
       </c>
-      <c r="F46" s="21" t="inlineStr">
+      <c r="F46" s="23" t="inlineStr">
         <is>
           <t>새로 추가: 모터 진동으로 풀림 방지 (PLA 에는 쓰지 않음)</t>
         </is>
       </c>
-      <c r="G46" s="21" t="inlineStr"/>
-      <c r="H46" s="21" t="inlineStr">
+      <c r="G46" s="23" t="inlineStr"/>
+      <c r="H46" s="23" t="inlineStr">
         <is>
           <t>검색 결과 2026-10-22 (화면 미확인)</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="21" t="n">
+    <row r="47" ht="35" customHeight="1" s="15">
+      <c r="A47" s="23" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="21" t="inlineStr">
+      <c r="B47" s="23" t="inlineStr">
         <is>
           <t>열수축 튜브 세트</t>
         </is>
       </c>
-      <c r="C47" s="21" t="inlineStr">
+      <c r="C47" s="23" t="inlineStr">
         <is>
           <t>530개</t>
         </is>
       </c>
-      <c r="D47" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" s="21" t="inlineStr">
+      <c r="D47" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="23" t="inlineStr">
         <is>
           <t>홀센서·가변저항·스위치 납땜부 절연</t>
         </is>
       </c>
-      <c r="F47" s="21" t="inlineStr">
+      <c r="F47" s="23" t="inlineStr">
         <is>
           <t>새로 추가</t>
         </is>
       </c>
-      <c r="G47" s="21" t="inlineStr"/>
-      <c r="H47" s="21" t="inlineStr">
+      <c r="G47" s="23" t="inlineStr"/>
+      <c r="H47" s="23" t="inlineStr">
         <is>
           <t>추정 (견적·옵션 확인 후 확정)</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="21" t="n">
+    <row r="48" ht="35" customHeight="1" s="15">
+      <c r="A48" s="23" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="21" t="inlineStr">
+      <c r="B48" s="23" t="inlineStr">
         <is>
           <t>케이블 타이</t>
         </is>
       </c>
-      <c r="C48" s="21" t="inlineStr">
+      <c r="C48" s="23" t="inlineStr">
         <is>
           <t>100개</t>
         </is>
       </c>
-      <c r="D48" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" s="21" t="inlineStr">
+      <c r="D48" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="23" t="inlineStr">
         <is>
           <t>배선 정리 (돌아가는 부품에 안 닿게)</t>
         </is>
       </c>
-      <c r="F48" s="21" t="inlineStr">
+      <c r="F48" s="23" t="inlineStr">
         <is>
           <t>새로 추가</t>
         </is>
       </c>
-      <c r="G48" s="21" t="inlineStr"/>
-      <c r="H48" s="21" t="inlineStr">
+      <c r="G48" s="23" t="inlineStr"/>
+      <c r="H48" s="23" t="inlineStr">
         <is>
           <t>추정 (견적·옵션 확인 후 확정)</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="21" t="n">
+    <row r="49" ht="35" customHeight="1" s="15">
+      <c r="A49" s="23" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="21" t="inlineStr">
+      <c r="B49" s="23" t="inlineStr">
         <is>
           <t>신호선 22AWG 연선</t>
         </is>
       </c>
-      <c r="C49" s="21" t="inlineStr">
+      <c r="C49" s="23" t="inlineStr">
         <is>
           <t>6색, 색마다 5m</t>
         </is>
       </c>
-      <c r="D49" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" s="21" t="inlineStr">
+      <c r="D49" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="23" t="inlineStr">
         <is>
           <t>페달·핸들 가변저항, 홀센서 → 아두이노 (점퍼선 40cm 로 안 닿는 곳)</t>
         </is>
       </c>
-      <c r="F49" s="21" t="inlineStr">
+      <c r="F49" s="23" t="inlineStr">
         <is>
           <t>새로 추가</t>
         </is>
       </c>
-      <c r="G49" s="21" t="inlineStr">
+      <c r="G49" s="23" t="inlineStr">
         <is>
           <t>m 단위 판매 → 색마다 5m</t>
         </is>
       </c>
-      <c r="H49" s="21" t="inlineStr">
+      <c r="H49" s="23" t="inlineStr">
         <is>
           <t>추정 (견적·옵션 확인 후 확정)</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="21" t="n">
+    <row r="50" ht="35" customHeight="1" s="15">
+      <c r="A50" s="23" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="21" t="inlineStr">
+      <c r="B50" s="23" t="inlineStr">
         <is>
           <t>디지털 멀티미터 (오토 레인지)</t>
         </is>
       </c>
-      <c r="C50" s="21" t="inlineStr"/>
-      <c r="D50" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" s="21" t="inlineStr">
+      <c r="C50" s="23" t="inlineStr"/>
+      <c r="D50" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="23" t="inlineStr">
         <is>
           <t>퓨즈·릴레이·스위치·센서 배선 점검</t>
         </is>
       </c>
-      <c r="F50" s="21" t="inlineStr">
+      <c r="F50" s="23" t="inlineStr">
         <is>
           <t>새로 추가 (학교에 있으면 뺌)</t>
         </is>
       </c>
-      <c r="G50" s="21" t="inlineStr"/>
-      <c r="H50" s="21" t="inlineStr">
+      <c r="G50" s="23" t="inlineStr"/>
+      <c r="H50" s="23" t="inlineStr">
         <is>
           <t>검색 결과 2026-10-22 (화면 미확인)</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="21" t="n">
+    <row r="51" ht="35" customHeight="1" s="15">
+      <c r="A51" s="23" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="21" t="inlineStr">
+      <c r="B51" s="23" t="inlineStr">
         <is>
           <t>HSS 드릴 날 세트</t>
         </is>
       </c>
-      <c r="C51" s="21" t="inlineStr">
+      <c r="C51" s="23" t="inlineStr">
         <is>
           <t>19개 (1~10mm)</t>
         </is>
       </c>
-      <c r="D51" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" s="21" t="inlineStr">
+      <c r="D51" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="23" t="inlineStr">
         <is>
           <t>MDF 목재나사 밑구멍 Ø2.5, 아크릴 Ø3.4</t>
         </is>
       </c>
-      <c r="F51" s="21" t="inlineStr">
+      <c r="F51" s="23" t="inlineStr">
         <is>
           <t>새로 추가 (보유한 것은 Ø3.4 하나)</t>
         </is>
       </c>
-      <c r="G51" s="21" t="inlineStr"/>
-      <c r="H51" s="21" t="inlineStr">
+      <c r="G51" s="23" t="inlineStr"/>
+      <c r="H51" s="23" t="inlineStr">
         <is>
           <t>검색 결과 2026-10-22 (화면 미확인)</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="21" t="n">
+    <row r="52" ht="35" customHeight="1" s="15">
+      <c r="A52" s="23" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="21" t="inlineStr">
+      <c r="B52" s="23" t="inlineStr">
         <is>
           <t>아두이노 레오나르도 R3 + USB 케이블</t>
         </is>
       </c>
-      <c r="C52" s="21" t="inlineStr">
+      <c r="C52" s="23" t="inlineStr">
         <is>
           <t>ATmega32u4</t>
         </is>
       </c>
-      <c r="D52" s="21" t="n">
+      <c r="D52" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E52" s="21" t="inlineStr">
+      <c r="E52" s="23" t="inlineStr">
         <is>
           <t>게임 입력·모터 허가 1 + 여분 1</t>
         </is>
       </c>
-      <c r="F52" s="21" t="inlineStr">
+      <c r="F52" s="23" t="inlineStr">
         <is>
           <t>여분 추가 (전시 중 고장 대비)</t>
         </is>
       </c>
-      <c r="G52" s="21" t="inlineStr"/>
-      <c r="H52" s="21" t="inlineStr">
+      <c r="G52" s="23" t="inlineStr"/>
+      <c r="H52" s="23" t="inlineStr">
         <is>
           <t>v3 단가</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="21" t="n">
+    <row r="53" ht="20" customHeight="1" s="15">
+      <c r="A53" s="23" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="21" t="inlineStr">
+      <c r="B53" s="23" t="inlineStr">
         <is>
           <t>홀센서 A3144</t>
         </is>
       </c>
-      <c r="C53" s="21" t="inlineStr">
+      <c r="C53" s="23" t="inlineStr">
         <is>
           <t>3핀</t>
         </is>
       </c>
-      <c r="D53" s="21" t="n">
+      <c r="D53" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="E53" s="21" t="inlineStr">
+      <c r="E53" s="23" t="inlineStr">
         <is>
           <t>기어 위치 6 · 출력 rpm 1 + 여분 3</t>
         </is>
       </c>
-      <c r="F53" s="21" t="inlineStr">
+      <c r="F53" s="23" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G53" s="21" t="inlineStr"/>
-      <c r="H53" s="21" t="inlineStr">
+      <c r="G53" s="23" t="inlineStr"/>
+      <c r="H53" s="23" t="inlineStr">
         <is>
           <t>v3 단가</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="21" t="n">
+    <row r="54" ht="35" customHeight="1" s="15">
+      <c r="A54" s="23" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="21" t="inlineStr">
+      <c r="B54" s="23" t="inlineStr">
         <is>
           <t>네오디뮴 자석</t>
         </is>
       </c>
-      <c r="C54" s="21" t="inlineStr">
+      <c r="C54" s="23" t="inlineStr">
         <is>
           <t>Ø6×3, 40개</t>
         </is>
       </c>
-      <c r="D54" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" s="21" t="inlineStr">
+      <c r="D54" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" s="23" t="inlineStr">
         <is>
           <t>러그 3 · 표시 바퀴 4 + 여분</t>
         </is>
       </c>
-      <c r="F54" s="21" t="inlineStr">
+      <c r="F54" s="23" t="inlineStr">
         <is>
           <t>디바이스마트 10개 대신</t>
         </is>
       </c>
-      <c r="G54" s="21" t="inlineStr"/>
-      <c r="H54" s="21" t="inlineStr">
+      <c r="G54" s="23" t="inlineStr"/>
+      <c r="H54" s="23" t="inlineStr">
         <is>
           <t>검색 결과 2026-10-22 (화면 미확인)</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="21" t="n">
+    <row r="55" ht="50" customHeight="1" s="15">
+      <c r="A55" s="23" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="21" t="inlineStr">
+      <c r="B55" s="23" t="inlineStr">
         <is>
           <t>가변저항 B10K WH148</t>
         </is>
       </c>
-      <c r="C55" s="21" t="inlineStr">
+      <c r="C55" s="23" t="inlineStr">
         <is>
           <t>하프(D)축 Ø6 15mm, 3핀, 부싱 M7</t>
         </is>
       </c>
-      <c r="D55" s="21" t="n">
+      <c r="D55" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E55" s="21" t="inlineStr">
+      <c r="E55" s="23" t="inlineStr">
         <is>
           <t>클러치·브레이크 페달 2 · 핸들 1 + 여분 2</t>
         </is>
       </c>
-      <c r="F55" s="21" t="inlineStr">
+      <c r="F55" s="23" t="inlineStr">
         <is>
           <t>디바이스마트 P160 대신. 축이 톱니(널링)가 아닌 D축이어야 페달 팔에 맞음</t>
         </is>
       </c>
-      <c r="G55" s="21" t="inlineStr">
+      <c r="G55" s="23" t="inlineStr">
         <is>
           <t>상품명에 "하프 샤프트 15mm"·B10K, 노브 없는 것. 도착하면 축 치수 재고 80·82 출력</t>
         </is>
       </c>
-      <c r="H55" s="21" t="inlineStr">
+      <c r="H55" s="23" t="inlineStr">
         <is>
           <t>검색 결과 2026-10-22 (화면 미확인), 1개 값인지 확인</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="21" t="n">
+    <row r="56" ht="20" customHeight="1" s="15">
+      <c r="A56" s="23" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="21" t="inlineStr">
+      <c r="B56" s="23" t="inlineStr">
         <is>
           <t>마이크로스위치 KW-11-3Z</t>
         </is>
       </c>
-      <c r="C56" s="21" t="inlineStr">
+      <c r="C56" s="23" t="inlineStr">
         <is>
           <t>레버형</t>
         </is>
       </c>
-      <c r="D56" s="21" t="n">
+      <c r="D56" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E56" s="21" t="inlineStr">
+      <c r="E56" s="23" t="inlineStr">
         <is>
           <t>덮개 열림 감지 1 + 여분 1</t>
         </is>
       </c>
-      <c r="F56" s="21" t="inlineStr">
+      <c r="F56" s="23" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G56" s="21" t="inlineStr"/>
-      <c r="H56" s="21" t="inlineStr">
+      <c r="G56" s="23" t="inlineStr"/>
+      <c r="H56" s="23" t="inlineStr">
         <is>
           <t>v3 단가</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="21" t="n">
+    <row r="57" ht="20" customHeight="1" s="15">
+      <c r="A57" s="23" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="21" t="inlineStr">
+      <c r="B57" s="23" t="inlineStr">
         <is>
           <t>점퍼 케이블 M-F</t>
         </is>
       </c>
-      <c r="C57" s="21" t="inlineStr">
+      <c r="C57" s="23" t="inlineStr">
         <is>
           <t>40P 40cm</t>
         </is>
       </c>
-      <c r="D57" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" s="21" t="inlineStr">
+      <c r="D57" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="23" t="inlineStr">
         <is>
           <t>센서 배선</t>
         </is>
       </c>
-      <c r="F57" s="21" t="inlineStr">
+      <c r="F57" s="23" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G57" s="21" t="inlineStr"/>
-      <c r="H57" s="21" t="inlineStr">
+      <c r="G57" s="23" t="inlineStr"/>
+      <c r="H57" s="23" t="inlineStr">
         <is>
           <t>v3 단가</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="21" t="n">
+    <row r="58" ht="35" customHeight="1" s="15">
+      <c r="A58" s="23" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="21" t="inlineStr">
+      <c r="B58" s="23" t="inlineStr">
         <is>
           <t>만능기판</t>
         </is>
       </c>
-      <c r="C58" s="21" t="inlineStr">
+      <c r="C58" s="23" t="inlineStr">
         <is>
           <t>양면, 묶음</t>
         </is>
       </c>
-      <c r="D58" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" s="21" t="inlineStr">
+      <c r="D58" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" s="23" t="inlineStr">
         <is>
           <t>센서 배선 기판 (실수하면 새 판)</t>
         </is>
       </c>
-      <c r="F58" s="21" t="inlineStr">
+      <c r="F58" s="23" t="inlineStr">
         <is>
           <t>디바이스마트 1장 대신</t>
         </is>
       </c>
-      <c r="G58" s="21" t="inlineStr"/>
-      <c r="H58" s="21" t="inlineStr">
+      <c r="G58" s="23" t="inlineStr"/>
+      <c r="H58" s="23" t="inlineStr">
         <is>
           <t>검색 결과 2026-10-22 (화면 미확인)</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="21" t="n">
+    <row r="59" ht="35" customHeight="1" s="15">
+      <c r="A59" s="23" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="21" t="inlineStr">
+      <c r="B59" s="23" t="inlineStr">
         <is>
           <t>자동차 릴레이 12V 40A + 소켓</t>
         </is>
       </c>
-      <c r="C59" s="21" t="inlineStr">
+      <c r="C59" s="23" t="inlineStr">
         <is>
           <t>4핀, 배선된 소켓</t>
         </is>
       </c>
-      <c r="D59" s="21" t="n">
+      <c r="D59" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E59" s="21" t="inlineStr">
+      <c r="E59" s="23" t="inlineStr">
         <is>
           <t>모터 주 스위치 1 + 여분 1</t>
         </is>
       </c>
-      <c r="F59" s="21" t="inlineStr">
+      <c r="F59" s="23" t="inlineStr">
         <is>
           <t>여분 추가</t>
         </is>
       </c>
-      <c r="G59" s="21" t="inlineStr"/>
-      <c r="H59" s="21" t="inlineStr">
+      <c r="G59" s="23" t="inlineStr"/>
+      <c r="H59" s="23" t="inlineStr">
         <is>
           <t>확인 2026-10-20</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="21" t="n">
+    <row r="60" ht="35" customHeight="1" s="15">
+      <c r="A60" s="23" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="21" t="inlineStr">
+      <c r="B60" s="23" t="inlineStr">
         <is>
           <t>블레이드 퓨즈 + 인라인 홀더 세트</t>
         </is>
       </c>
-      <c r="C60" s="21" t="inlineStr">
+      <c r="C60" s="23" t="inlineStr">
         <is>
           <t>15A 포함, 홀더 4 + 퓨즈 12</t>
         </is>
       </c>
-      <c r="D60" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" s="21" t="inlineStr">
+      <c r="D60" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="23" t="inlineStr">
         <is>
           <t>배터리 + 단자 바로 옆</t>
         </is>
       </c>
-      <c r="F60" s="21" t="inlineStr">
+      <c r="F60" s="23" t="inlineStr">
         <is>
           <t>그대로 (여분 퓨즈 포함)</t>
         </is>
       </c>
-      <c r="G60" s="21" t="inlineStr"/>
-      <c r="H60" s="21" t="inlineStr">
+      <c r="G60" s="23" t="inlineStr"/>
+      <c r="H60" s="23" t="inlineStr">
         <is>
           <t>확인 2026-10-20</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="21" t="n">
+    <row r="61" ht="35" customHeight="1" s="15">
+      <c r="A61" s="23" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="21" t="inlineStr">
+      <c r="B61" s="23" t="inlineStr">
         <is>
           <t>비상정지 스위치 22mm</t>
         </is>
       </c>
-      <c r="C61" s="21" t="inlineStr">
+      <c r="C61" s="23" t="inlineStr">
         <is>
           <t>버섯형, 1a1b, 명판 포함 (A20B-V4E11R)</t>
         </is>
       </c>
-      <c r="D61" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" s="21" t="inlineStr">
+      <c r="D61" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="23" t="inlineStr">
         <is>
           <t>운영자 비상 차단 (릴레이 코일 회로, b접점)</t>
         </is>
       </c>
-      <c r="F61" s="21" t="inlineStr">
+      <c r="F61" s="23" t="inlineStr">
         <is>
           <t>디바이스마트 KGE-C4R1R 대신</t>
         </is>
       </c>
-      <c r="G61" s="21" t="inlineStr">
+      <c r="G61" s="23" t="inlineStr">
         <is>
           <t>b접점(1b) 있는지</t>
         </is>
       </c>
-      <c r="H61" s="21" t="inlineStr">
+      <c r="H61" s="23" t="inlineStr">
         <is>
           <t>검색 결과 2026-10-22 (화면 미확인)</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="21" t="n">
+    <row r="62" ht="35" customHeight="1" s="15">
+      <c r="A62" s="23" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="21" t="inlineStr">
+      <c r="B62" s="23" t="inlineStr">
         <is>
           <t>비상정지 스위치 박스</t>
         </is>
       </c>
-      <c r="C62" s="21" t="inlineStr">
+      <c r="C62" s="23" t="inlineStr">
         <is>
           <t>1구 (22mm 구멍)</t>
         </is>
       </c>
-      <c r="D62" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" s="21" t="inlineStr">
+      <c r="D62" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="23" t="inlineStr">
         <is>
           <t>비상정지 스위치를 넣어 운영자 앞 책상에 둠</t>
         </is>
       </c>
-      <c r="F62" s="21" t="inlineStr">
+      <c r="F62" s="23" t="inlineStr">
         <is>
           <t>새로 추가: 판에 25mm 구멍을 안 뚫어도 됨</t>
         </is>
       </c>
-      <c r="G62" s="21" t="inlineStr">
+      <c r="G62" s="23" t="inlineStr">
         <is>
           <t>옵션 1구, 구멍 22mm</t>
         </is>
       </c>
-      <c r="H62" s="21" t="inlineStr">
+      <c r="H62" s="23" t="inlineStr">
         <is>
           <t>검색 결과 2026-10-22 (화면 미확인)</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="21" t="n">
+    <row r="63" ht="35" customHeight="1" s="15">
+      <c r="A63" s="23" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="21" t="inlineStr">
+      <c r="B63" s="23" t="inlineStr">
         <is>
           <t>5V 릴레이 모듈 1채널</t>
         </is>
       </c>
-      <c r="C63" s="21" t="inlineStr">
+      <c r="C63" s="23" t="inlineStr">
         <is>
           <t>DM106</t>
         </is>
       </c>
-      <c r="D63" s="21" t="n">
+      <c r="D63" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E63" s="21" t="inlineStr">
+      <c r="E63" s="23" t="inlineStr">
         <is>
           <t>아두이노 감시 → 주 릴레이 코일 차단 1 + 여분 1</t>
         </is>
       </c>
-      <c r="F63" s="21" t="inlineStr">
+      <c r="F63" s="23" t="inlineStr">
         <is>
           <t>디바이스마트 로우 트리거 모듈 대신</t>
         </is>
       </c>
-      <c r="G63" s="21" t="inlineStr">
+      <c r="G63" s="23" t="inlineStr">
         <is>
           <t>하이/로우 트리거는 펌웨어 RELAY_ACTIVE_LOW 로 맞춤</t>
         </is>
       </c>
-      <c r="H63" s="21" t="inlineStr">
+      <c r="H63" s="23" t="inlineStr">
         <is>
           <t>추정 (견적·옵션 확인 후 확정)</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="21" t="n">
+    <row r="64" ht="35" customHeight="1" s="15">
+      <c r="A64" s="23" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="21" t="inlineStr">
+      <c r="B64" s="23" t="inlineStr">
         <is>
           <t>다이오드 1N4007</t>
         </is>
       </c>
-      <c r="C64" s="21" t="inlineStr">
+      <c r="C64" s="23" t="inlineStr">
         <is>
           <t>10개</t>
         </is>
       </c>
-      <c r="D64" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" s="21" t="inlineStr">
+      <c r="D64" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="23" t="inlineStr">
         <is>
           <t>주 릴레이 코일 역기전력 흡수 + 여분</t>
         </is>
       </c>
-      <c r="F64" s="21" t="inlineStr">
+      <c r="F64" s="23" t="inlineStr">
         <is>
           <t>디바이스마트 대신</t>
         </is>
       </c>
-      <c r="G64" s="21" t="inlineStr"/>
-      <c r="H64" s="21" t="inlineStr">
+      <c r="G64" s="23" t="inlineStr"/>
+      <c r="H64" s="23" t="inlineStr">
         <is>
           <t>검색 결과 2026-10-22 (화면 미확인)</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="21" t="n">
+    <row r="65" ht="35" customHeight="1" s="15">
+      <c r="A65" s="23" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="21" t="inlineStr">
+      <c r="B65" s="23" t="inlineStr">
         <is>
           <t>저항 세트 1/4W</t>
         </is>
       </c>
-      <c r="C65" s="21" t="inlineStr">
+      <c r="C65" s="23" t="inlineStr">
         <is>
           <t>30종 × 20개 (10kΩ·4.7kΩ 포함)</t>
         </is>
       </c>
-      <c r="D65" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" s="21" t="inlineStr">
+      <c r="D65" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="23" t="inlineStr">
         <is>
           <t>안전 회로 감지 (비상정지·덮개 뒤 12V → 아두이노 A4)</t>
         </is>
       </c>
-      <c r="F65" s="21" t="inlineStr">
+      <c r="F65" s="23" t="inlineStr">
         <is>
           <t>디바이스마트 2종 대신 세트</t>
         </is>
       </c>
-      <c r="G65" s="21" t="inlineStr">
+      <c r="G65" s="23" t="inlineStr">
         <is>
           <t>10kΩ·4.7kΩ 들어 있는지</t>
         </is>
       </c>
-      <c r="H65" s="21" t="inlineStr">
+      <c r="H65" s="23" t="inlineStr">
         <is>
           <t>검색 결과 2026-10-22 (화면 미확인)</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="21" t="n">
+    <row r="66" ht="35" customHeight="1" s="15">
+      <c r="A66" s="23" t="n">
         <v>65</v>
       </c>
-      <c r="B66" s="21" t="inlineStr">
+      <c r="B66" s="23" t="inlineStr">
         <is>
           <t>실리콘 전선 16AWG 빨강·검정</t>
         </is>
       </c>
-      <c r="C66" s="21" t="inlineStr">
+      <c r="C66" s="23" t="inlineStr">
         <is>
           <t>1m 세트</t>
         </is>
       </c>
-      <c r="D66" s="21" t="n">
+      <c r="D66" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E66" s="21" t="inlineStr">
+      <c r="E66" s="23" t="inlineStr">
         <is>
           <t>배터리-퓨즈-릴레이-모터 드라이버 (2m 필요 + 여분 1m)</t>
         </is>
       </c>
-      <c r="F66" s="21" t="inlineStr">
+      <c r="F66" s="23" t="inlineStr">
         <is>
           <t>2 → 3</t>
         </is>
       </c>
-      <c r="G66" s="21" t="inlineStr"/>
-      <c r="H66" s="21" t="inlineStr">
+      <c r="G66" s="23" t="inlineStr"/>
+      <c r="H66" s="23" t="inlineStr">
         <is>
           <t>확인 2026-10-20</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="21" t="n">
+    <row r="67" ht="35" customHeight="1" s="15">
+      <c r="A67" s="23" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="21" t="inlineStr">
+      <c r="B67" s="23" t="inlineStr">
         <is>
           <t>절연 암 평형 단자 250 (6.3mm)</t>
         </is>
       </c>
-      <c r="C67" s="21" t="inlineStr">
+      <c r="C67" s="23" t="inlineStr">
         <is>
           <t>22~16AWG, 2개 봉</t>
         </is>
       </c>
-      <c r="D67" s="21" t="n">
+      <c r="D67" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E67" s="21" t="inlineStr">
+      <c r="E67" s="23" t="inlineStr">
         <is>
           <t>퓨즈 홀더·릴레이 소켓 연결 + 여분 (압착 실수)</t>
         </is>
       </c>
-      <c r="F67" s="21" t="inlineStr">
+      <c r="F67" s="23" t="inlineStr">
         <is>
           <t>3 → 5</t>
         </is>
       </c>
-      <c r="G67" s="21" t="inlineStr"/>
-      <c r="H67" s="21" t="inlineStr">
+      <c r="G67" s="23" t="inlineStr"/>
+      <c r="H67" s="23" t="inlineStr">
         <is>
           <t>확인 2026-10-20</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="21" t="n">
+    <row r="68" ht="50" customHeight="1" s="15">
+      <c r="A68" s="23" t="n">
         <v>67</v>
       </c>
-      <c r="B68" s="21" t="inlineStr">
+      <c r="B68" s="23" t="inlineStr">
         <is>
           <t>배송비</t>
         </is>
       </c>
-      <c r="C68" s="21" t="inlineStr">
+      <c r="C68" s="23" t="inlineStr">
         <is>
           <t>판매처별 합계</t>
         </is>
       </c>
-      <c r="D68" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E68" s="21" t="inlineStr">
+      <c r="D68" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="23" t="inlineStr">
         <is>
           <t>쿠팡 기존 47,200 + 11번가 13곳 40,000 + G마켓 4곳 12,000 + 새 쿠팡 2곳·스프링 9,000</t>
         </is>
       </c>
-      <c r="F68" s="21" t="inlineStr"/>
-      <c r="G68" s="21" t="inlineStr"/>
-      <c r="H68" s="21" t="inlineStr">
+      <c r="F68" s="23" t="inlineStr"/>
+      <c r="G68" s="23" t="inlineStr"/>
+      <c r="H68" s="23" t="inlineStr">
         <is>
           <t>추정 (견적·옵션 확인 후 확정)</t>
         </is>

--- a/v4/창체_물품계획서_RPM.xlsx
+++ b/v4/창체_물품계획서_RPM.xlsx
@@ -2006,7 +2006,7 @@
         <v>75900</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G41" s="17">
         <f>F41*E41</f>

--- a/v4/창체_물품계획서_RPM.xlsx
+++ b/v4/창체_물품계획서_RPM.xlsx
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="6.5" customWidth="1" style="10" min="1" max="1"/>
@@ -684,7 +684,7 @@
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/2569692102</t>
+          <t>https://www.11st.co.kr/products/1432577678</t>
         </is>
       </c>
     </row>
@@ -739,11 +739,11 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>연마봉 Ø12 S45C 1m (열처리 안 된 것) (435·358·160 으로 절단)</t>
+          <t>SM45C 마봉 Ø12 1m 6개 (열처리 안 된 것) (Ø12 × 1000, 6개 세트)</t>
         </is>
       </c>
       <c r="E5" s="17" t="n">
-        <v>16000</v>
+        <v>39000</v>
       </c>
       <c r="F5" s="12" t="n">
         <v>1</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>https://item.gmarket.co.kr/Item?goodscode=2295287294</t>
+          <t>https://www.coupang.com/vp/products/9472297916</t>
         </is>
       </c>
     </row>
@@ -774,14 +774,14 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>연마봉 Ø12 S45C 1m (여분, 열처리 안 된 것) (자르지 않음)</t>
+          <t>스텐 환봉 Ø6 1m (자르지 않은 1m (371mm 2개씩 직접 자름))</t>
         </is>
       </c>
       <c r="E6" s="17" t="n">
-        <v>16000</v>
+        <v>2800</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="17">
         <f>F6*E6</f>
@@ -789,11 +789,11 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>https://item.gmarket.co.kr/Item?goodscode=2295287294</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="24.9" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/7575963441</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="35" customHeight="1" s="15">
       <c r="A7" s="16" t="n">
         <v>5</v>
       </c>
@@ -809,11 +809,11 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>연마봉 Ø12 S45C 10cm (55 로 절단)</t>
+          <t>강철 평행핀 Ø5×25 (100개, 공차 0~+0.01)</t>
         </is>
       </c>
       <c r="E7" s="17" t="n">
-        <v>1600</v>
+        <v>27000</v>
       </c>
       <c r="F7" s="12" t="n">
         <v>1</v>
@@ -824,7 +824,7 @@
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>https://item.gmarket.co.kr/Item?goodscode=2295287294</t>
+          <t>https://www.coupang.com/vp/products/9743421687</t>
         </is>
       </c>
     </row>
@@ -844,14 +844,14 @@
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>스텐 환봉 Ø6 1m (371mm 2개로 절단)</t>
+          <t>강철 평행핀 Ø5×40 (공차 0~+0.01)</t>
         </is>
       </c>
       <c r="E8" s="17" t="n">
-        <v>4000</v>
+        <v>440</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G8" s="17">
         <f>F8*E8</f>
@@ -859,7 +859,7 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>https://item.gmarket.co.kr/Item?goodscode=692264521</t>
+          <t>https://www.coupang.com/vp/products/8532354386</t>
         </is>
       </c>
     </row>
@@ -879,11 +879,11 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>강철 평행핀 Ø5×25 (100개, 공차 0~+0.01)</t>
+          <t>고무 호스 (안지름 5 × 바깥지름 10, 약 2m)</t>
         </is>
       </c>
       <c r="E9" s="17" t="n">
-        <v>27000</v>
+        <v>8900</v>
       </c>
       <c r="F9" s="12" t="n">
         <v>1</v>
@@ -894,7 +894,7 @@
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9743421687</t>
+          <t>https://www.coupang.com/vp/products/8558801755</t>
         </is>
       </c>
     </row>
@@ -914,14 +914,14 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>강철 평행핀 Ø5×40 (공차 0~+0.01)</t>
+          <t>큰 와셔 DIN9021 M16 스텐 (17×50×3)</t>
         </is>
       </c>
       <c r="E10" s="17" t="n">
-        <v>440</v>
+        <v>710</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G10" s="17">
         <f>F10*E10</f>
@@ -929,11 +929,11 @@
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8532354386</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="35" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/6305734042</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24.9" customHeight="1" s="15">
       <c r="A11" s="16" t="n">
         <v>9</v>
       </c>
@@ -949,11 +949,11 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>NBR 고무 호스 (안지름 5 × 바깥지름 10, 약 2m)</t>
+          <t>코르크 시트 (2mm, A4 2매)</t>
         </is>
       </c>
       <c r="E11" s="17" t="n">
-        <v>8900</v>
+        <v>1890</v>
       </c>
       <c r="F11" s="12" t="n">
         <v>1</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8558801755</t>
+          <t>https://www.coupang.com/vp/products/4845669553</t>
         </is>
       </c>
     </row>
@@ -984,14 +984,14 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>큰 와셔 DIN9021 M16 스텐 (17×50×3)</t>
+          <t>강구 (Ø6, 50개)</t>
         </is>
       </c>
       <c r="E12" s="17" t="n">
-        <v>710</v>
+        <v>3500</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" s="17">
         <f>F12*E12</f>
@@ -999,11 +999,11 @@
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6305734042</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="24.9" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/9638493021</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="35" customHeight="1" s="15">
       <c r="A13" s="16" t="n">
         <v>11</v>
       </c>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>코르크 시트 (2mm, A4 2매)</t>
+          <t>샤프트 칼라 Ø6 (무두볼트 고정) (안 6 · 바깥 12 · 폭 6)</t>
         </is>
       </c>
       <c r="E13" s="17" t="n">
-        <v>1890</v>
+        <v>1500</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G13" s="17">
         <f>F13*E13</f>
@@ -1034,11 +1034,11 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/4845669553</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="24.9" customHeight="1" s="15">
+          <t>https://item.gmarket.co.kr/Item?goodscode=4101441390</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="35" customHeight="1" s="15">
       <c r="A14" s="16" t="n">
         <v>12</v>
       </c>
@@ -1054,14 +1054,14 @@
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>강구 (Ø6, 50개)</t>
+          <t>압축 스프링 SUS304 (C252 대신) (선경 1.5 · 외경 18 · 자유장 25)</t>
         </is>
       </c>
       <c r="E14" s="17" t="n">
-        <v>3500</v>
+        <v>1590</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G14" s="17">
         <f>F14*E14</f>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9638493021</t>
+          <t>https://www.coupang.com/vp/products/4387963066</t>
         </is>
       </c>
     </row>
@@ -1089,14 +1089,14 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>샤프트 칼라 Ø6 (무두볼트 고정) (안 6 · 바깥 12 · 폭 6)</t>
+          <t>압축 스프링 SUS304 (C147 대신) (선경 0.4 · 외경 5 · 자유장 10)</t>
         </is>
       </c>
       <c r="E15" s="17" t="n">
-        <v>1500</v>
+        <v>1100</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G15" s="17">
         <f>F15*E15</f>
@@ -1104,11 +1104,11 @@
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>https://m.gmarket.co.kr/vi/product/4101441390</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/8501265889</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="24.9" customHeight="1" s="15">
       <c r="A16" s="16" t="n">
         <v>14</v>
       </c>
@@ -1124,14 +1124,14 @@
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>압축 스프링 (C252 대신, 기성품) (외경 17.0~18.5 · 안지름 12.8 이상 · 자유장 30~36 · 선경 1.5~1.7 · 밀착 높이 15 이하 · 권수가 보일 것)</t>
+          <t>M3 렌치볼트 스텐 (M3×8)</t>
         </is>
       </c>
       <c r="E16" s="17" t="n">
-        <v>1500</v>
+        <v>50</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G16" s="17">
         <f>F16*E16</f>
@@ -1139,11 +1139,11 @@
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=압축스프링 외경18</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/6455358137</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24.9" customHeight="1" s="15">
       <c r="A17" s="16" t="n">
         <v>15</v>
       </c>
@@ -1159,14 +1159,14 @@
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>압축 스프링 (C147 대신, 기성품) (외경 4.5~5.5 · 자유장 9~12 · 선경 0.4~0.5 · 밀착 높이 4.5 이하 · 권수가 보일 것)</t>
+          <t>M3 렌치볼트 스텐 (M3×10)</t>
         </is>
       </c>
       <c r="E17" s="17" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G17" s="17">
         <f>F17*E17</f>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=스텐 압축스프링 선경0.5 외경5</t>
+          <t>https://www.coupang.com/vp/products/6455358137</t>
         </is>
       </c>
     </row>
@@ -1194,14 +1194,14 @@
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>M3 렌치볼트 (M3×8)</t>
+          <t>M3 렌치볼트 스텐 (M3×12)</t>
         </is>
       </c>
       <c r="E18" s="17" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="G18" s="17">
         <f>F18*E18</f>
@@ -1229,14 +1229,14 @@
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>M3 렌치볼트 (M3×10)</t>
+          <t>M3 렌치볼트 스텐 (M3×16)</t>
         </is>
       </c>
       <c r="E19" s="17" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" s="17">
         <f>F19*E19</f>
@@ -1264,14 +1264,14 @@
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>M3 렌치볼트 (M3×12)</t>
+          <t>M3 렌치볼트 스텐 (M3×20)</t>
         </is>
       </c>
       <c r="E20" s="17" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="G20" s="17">
         <f>F20*E20</f>
@@ -1299,14 +1299,14 @@
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>M3 렌치볼트 (M3×16)</t>
+          <t>M3 렌치볼트 스텐 (M3×25)</t>
         </is>
       </c>
       <c r="E21" s="17" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G21" s="17">
         <f>F21*E21</f>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>M3 렌치볼트 + 육각너트 (M3×20)</t>
+          <t>M3 렌치볼트 스텐 (M3×50)</t>
         </is>
       </c>
       <c r="E22" s="17" t="n">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G22" s="17">
         <f>F22*E22</f>
@@ -1369,14 +1369,14 @@
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>M3 렌치볼트 (M3×25)</t>
+          <t>M3 육각너트 스텐 (M3 (맞변 5.5))</t>
         </is>
       </c>
       <c r="E23" s="17" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G23" s="17">
         <f>F23*E23</f>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6455358137</t>
+          <t>https://www.coupang.com/vp/products/8532240860</t>
         </is>
       </c>
     </row>
@@ -1404,11 +1404,11 @@
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>M3 렌치볼트 (M3×50)</t>
+          <t>M3 무두볼트 스텐 (오목끝) (M3×8)</t>
         </is>
       </c>
       <c r="E24" s="17" t="n">
-        <v>170</v>
+        <v>60</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>5</v>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6455358137</t>
+          <t>https://www.coupang.com/vp/products/7974822838</t>
         </is>
       </c>
     </row>
@@ -1439,14 +1439,14 @@
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>M3 무두볼트 (오목끝) (M3×8)</t>
+          <t>M3 평와셔 스텐 (바깥 8 × 두께 0.5)</t>
         </is>
       </c>
       <c r="E25" s="17" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G25" s="17">
         <f>F25*E25</f>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/7974822838</t>
+          <t>https://www.coupang.com/vp/products/7440529428</t>
         </is>
       </c>
     </row>
@@ -1474,11 +1474,11 @@
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>M3 육각너트 스텐 (M3 (맞변 5.5))</t>
+          <t>M4 렌치볼트 스텐 (M4×16)</t>
         </is>
       </c>
       <c r="E26" s="17" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>5</v>
@@ -1509,14 +1509,14 @@
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>M3 평와셔 스텐 (바깥 8 × 두께 0.5)</t>
+          <t>M4 렌치볼트 스텐 (M4×25)</t>
         </is>
       </c>
       <c r="E27" s="17" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G27" s="17">
         <f>F27*E27</f>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/7440529428</t>
+          <t>https://www.coupang.com/vp/products/6455358137</t>
         </is>
       </c>
     </row>
@@ -1544,14 +1544,14 @@
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>M4 렌치볼트 + 너트 (M4×16)</t>
+          <t>M4 렌치볼트 스텐 (M4×30)</t>
         </is>
       </c>
       <c r="E28" s="17" t="n">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="G28" s="17">
         <f>F28*E28</f>
@@ -1579,14 +1579,14 @@
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>M4 렌치볼트 + 너트 (M4×25)</t>
+          <t>M4 렌치볼트 스텐 (M4×60)</t>
         </is>
       </c>
       <c r="E29" s="17" t="n">
-        <v>160</v>
+        <v>290</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G29" s="17">
         <f>F29*E29</f>
@@ -1614,14 +1614,14 @@
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>M4 렌치볼트 + 너트 (M4×30)</t>
+          <t>M4 육각너트 스텐 (M4 (맞변 7))</t>
         </is>
       </c>
       <c r="E30" s="17" t="n">
-        <v>190</v>
+        <v>60</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G30" s="17">
         <f>F30*E30</f>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6455358137</t>
+          <t>https://www.coupang.com/vp/products/8531939792</t>
         </is>
       </c>
     </row>
@@ -1649,11 +1649,11 @@
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>M4 렌치볼트 + 너트 (M4×60)</t>
+          <t>M5 렌치볼트 스텐 (M5×10)</t>
         </is>
       </c>
       <c r="E31" s="17" t="n">
-        <v>350</v>
+        <v>110</v>
       </c>
       <c r="F31" s="12" t="n">
         <v>4</v>
@@ -1684,14 +1684,14 @@
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>M5 렌치볼트 + 너트 (M5×10)</t>
+          <t>M5 렌치볼트 스텐 (M5×20)</t>
         </is>
       </c>
       <c r="E32" s="17" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G32" s="17">
         <f>F32*E32</f>
@@ -1719,14 +1719,14 @@
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>M5 렌치볼트 + 너트 (M5×20)</t>
+          <t>M5 육각너트 스텐 (M5 (맞변 8))</t>
         </is>
       </c>
       <c r="E33" s="17" t="n">
-        <v>230</v>
+        <v>90</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G33" s="17">
         <f>F33*E33</f>
@@ -1734,11 +1734,11 @@
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6455358137</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="35" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/8531595719</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24.9" customHeight="1" s="15">
       <c r="A34" s="16" t="n">
         <v>32</v>
       </c>
@@ -1754,14 +1754,14 @@
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>M5 조정용 볼트 세트 (M5×8 3 + M5×12 3 + M5 평와셔 3)</t>
+          <t>M5 렌치볼트 스텐 (조정용) (M5×8)</t>
         </is>
       </c>
       <c r="E34" s="17" t="n">
-        <v>720</v>
+        <v>100</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G34" s="17">
         <f>F34*E34</f>
@@ -1789,14 +1789,14 @@
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>M5 렌치볼트 + 나일론 너트 (M5×70)</t>
+          <t>M5 렌치볼트 스텐 (조정용) (M5×12)</t>
         </is>
       </c>
       <c r="E35" s="17" t="n">
-        <v>550</v>
+        <v>110</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G35" s="17">
         <f>F35*E35</f>
@@ -1824,11 +1824,11 @@
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>M5 렌치볼트 + 나일론 너트 (M5×40)</t>
+          <t>M5 평와셔 스텐 (바깥 12 × 두께 0.5)</t>
         </is>
       </c>
       <c r="E36" s="17" t="n">
-        <v>380</v>
+        <v>30</v>
       </c>
       <c r="F36" s="12" t="n">
         <v>3</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6455358137</t>
+          <t>https://www.coupang.com/vp/products/7440529428</t>
         </is>
       </c>
     </row>
@@ -1859,14 +1859,14 @@
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>M6 렌치볼트 (M6×25)</t>
+          <t>M5 렌치볼트 스텐 (M5×70)</t>
         </is>
       </c>
       <c r="E37" s="17" t="n">
-        <v>210</v>
+        <v>470</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G37" s="17">
         <f>F37*E37</f>
@@ -1894,14 +1894,14 @@
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>M6 너트 (M6 (맞변 10))</t>
+          <t>M5 나일론 너트 스텐 (M5 (DIN985))</t>
         </is>
       </c>
       <c r="E38" s="17" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G38" s="17">
         <f>F38*E38</f>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/7687671245</t>
+          <t>https://www.coupang.com/vp/products/6280971320</t>
         </is>
       </c>
     </row>
@@ -1929,14 +1929,14 @@
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>M6 나일론 너트 (M6 (DIN985))</t>
+          <t>M6 렌치볼트 스텐 (M6×25)</t>
         </is>
       </c>
       <c r="E39" s="17" t="n">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G39" s="17">
         <f>F39*E39</f>
@@ -1944,11 +1944,11 @@
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6280971320</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="35" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/6455358137</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="24.9" customHeight="1" s="15">
       <c r="A40" s="16" t="n">
         <v>38</v>
       </c>
@@ -1964,14 +1964,14 @@
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>목재 나사 스텐 둥근머리 (4×16, 26개 봉)</t>
+          <t>M6 육각너트 스텐 (M6 (맞변 10))</t>
         </is>
       </c>
       <c r="E40" s="17" t="n">
-        <v>1150</v>
+        <v>60</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G40" s="17">
         <f>F40*E40</f>
@@ -1979,11 +1979,11 @@
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/7760964029</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="35" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/7687671245</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="24.9" customHeight="1" s="15">
       <c r="A41" s="16" t="n">
         <v>39</v>
       </c>
@@ -1999,14 +1999,14 @@
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>PLA 필라멘트 울티메이커 정품 (2.85mm, 750g)</t>
+          <t>M6 나일론 너트 스텐 (M6 (DIN985))</t>
         </is>
       </c>
       <c r="E41" s="17" t="n">
-        <v>75900</v>
+        <v>70</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G41" s="17">
         <f>F41*E41</f>
@@ -2014,11 +2014,11 @@
       </c>
       <c r="H41" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=울티메이커 PLA 2.85mm 750g</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="24.9" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/6280971320</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="35" customHeight="1" s="15">
       <c r="A42" s="16" t="n">
         <v>40</v>
       </c>
@@ -2034,11 +2034,11 @@
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>2액형 에폭시 접착제 (주사기형 25ml)</t>
+          <t>목재 나사 스텐 둥근머리 (4×16, 26개 봉)</t>
         </is>
       </c>
       <c r="E42" s="17" t="n">
-        <v>4440</v>
+        <v>1150</v>
       </c>
       <c r="F42" s="12" t="n">
         <v>2</v>
@@ -2049,11 +2049,11 @@
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/2725054</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="24.9" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/7760964029</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="35" customHeight="1" s="15">
       <c r="A43" s="16" t="n">
         <v>41</v>
       </c>
@@ -2069,14 +2069,14 @@
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>순간접착제 (젤 타입 2개)</t>
+          <t>PLA 필라멘트 울티메이커 정품 검정 (2.85mm, 750g)</t>
         </is>
       </c>
       <c r="E43" s="17" t="n">
-        <v>3000</v>
+        <v>75900</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G43" s="17">
         <f>F43*E43</f>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8643897709</t>
+          <t>https://www.coupang.com/vp/products/9783043879</t>
         </is>
       </c>
     </row>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>자전거 브레이크 케이블 세트 (속선 2 + 아우터 Ø5 + 끝 캡)</t>
+          <t>PLA 필라멘트 울티메이커 정품 주황 (2.85mm, 750g)</t>
         </is>
       </c>
       <c r="E44" s="17" t="n">
-        <v>6900</v>
+        <v>75900</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G44" s="17">
         <f>F44*E44</f>
@@ -2119,11 +2119,11 @@
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8305908512</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="24.9" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/9783044238</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="35" customHeight="1" s="15">
       <c r="A45" s="16" t="n">
         <v>43</v>
       </c>
@@ -2139,14 +2139,14 @@
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>MDF 판 (12T 300×1200 재단)</t>
+          <t>PLA 필라멘트 울티메이커 정품 파랑 (2.85mm, 750g)</t>
         </is>
       </c>
       <c r="E45" s="17" t="n">
-        <v>9600</v>
+        <v>75900</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G45" s="17">
         <f>F45*E45</f>
@@ -2154,11 +2154,11 @@
       </c>
       <c r="H45" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/71452005</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="24.9" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/9783043880</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="35" customHeight="1" s="15">
       <c r="A46" s="16" t="n">
         <v>44</v>
       </c>
@@ -2174,11 +2174,11 @@
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>투명 아크릴 3T 치수 재단 (250×321)</t>
+          <t>PLA 필라멘트 울티메이커 정품 노랑 (2.85mm, 750g)</t>
         </is>
       </c>
       <c r="E46" s="17" t="n">
-        <v>9000</v>
+        <v>75900</v>
       </c>
       <c r="F46" s="12" t="n">
         <v>1</v>
@@ -2189,11 +2189,11 @@
       </c>
       <c r="H46" s="12" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/4918717495</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="24.9" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/9783043850</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="35" customHeight="1" s="15">
       <c r="A47" s="16" t="n">
         <v>45</v>
       </c>
@@ -2209,14 +2209,14 @@
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>투명 아크릴 3T 치수 재단 (200×321)</t>
+          <t>2액형 에폭시 접착제 (주사기형 25ml, 2개 묶음)</t>
         </is>
       </c>
       <c r="E47" s="17" t="n">
-        <v>9000</v>
+        <v>7650</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G47" s="17">
         <f>F47*E47</f>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="H47" s="12" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/4918717495</t>
+          <t>https://www.coupang.com/vp/products/2725054</t>
         </is>
       </c>
     </row>
@@ -2244,11 +2244,11 @@
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>투명 아크릴 A3 3T (여분) (297×420)</t>
+          <t>순간접착제 (젤 타입 2개)</t>
         </is>
       </c>
       <c r="E48" s="17" t="n">
-        <v>9000</v>
+        <v>3000</v>
       </c>
       <c r="F48" s="12" t="n">
         <v>1</v>
@@ -2259,11 +2259,11 @@
       </c>
       <c r="H48" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9593337115</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="24.9" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/8643897709</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="35" customHeight="1" s="15">
       <c r="A49" s="16" t="n">
         <v>47</v>
       </c>
@@ -2279,11 +2279,11 @@
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>PTFE 합성 그리스 (슈퍼루브) (85g)</t>
+          <t>자전거 브레이크 케이블 세트 (속선 2 + 아우터 + 끝 캡)</t>
         </is>
       </c>
       <c r="E49" s="17" t="n">
-        <v>12000</v>
+        <v>6900</v>
       </c>
       <c r="F49" s="12" t="n">
         <v>1</v>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="H49" s="12" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/5099555102</t>
+          <t>https://www.coupang.com/vp/products/8305908512</t>
         </is>
       </c>
     </row>
@@ -2314,11 +2314,11 @@
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>나사 고정제 록타이트 243 (10ml)</t>
+          <t>MDF 판 (12T 300×1200 재단)</t>
         </is>
       </c>
       <c r="E50" s="17" t="n">
-        <v>7790</v>
+        <v>9600</v>
       </c>
       <c r="F50" s="12" t="n">
         <v>1</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="H50" s="12" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/7426834008</t>
+          <t>https://www.coupang.com/vp/products/71452005</t>
         </is>
       </c>
     </row>
@@ -2349,11 +2349,11 @@
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>열수축 튜브 세트 (여러 지름 묶음)</t>
+          <t>투명 아크릴 3T 치수 재단 (250×321)</t>
         </is>
       </c>
       <c r="E51" s="17" t="n">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="F51" s="12" t="n">
         <v>1</v>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="H51" s="12" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/2070330612</t>
+          <t>https://www.11st.co.kr/products/4918717495</t>
         </is>
       </c>
     </row>
@@ -2384,14 +2384,14 @@
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>케이블 타이 (100개)</t>
+          <t>투명 아크릴 3T 치수 재단 (200×321)</t>
         </is>
       </c>
       <c r="E52" s="17" t="n">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G52" s="17">
         <f>F52*E52</f>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="H52" s="12" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/2283460419</t>
+          <t>https://www.11st.co.kr/products/4918717495</t>
         </is>
       </c>
     </row>
@@ -2419,11 +2419,11 @@
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>신호선 22AWG 연선 (6색, 색마다 5m)</t>
+          <t>투명 아크릴 A3 3T (여분) (297×420)</t>
         </is>
       </c>
       <c r="E53" s="17" t="n">
-        <v>10000</v>
+        <v>9000</v>
       </c>
       <c r="F53" s="12" t="n">
         <v>1</v>
@@ -2434,11 +2434,11 @@
       </c>
       <c r="H53" s="12" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/679503128</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="35" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/9593337115</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="24.9" customHeight="1" s="15">
       <c r="A54" s="16" t="n">
         <v>52</v>
       </c>
@@ -2454,11 +2454,11 @@
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>디지털 캘리퍼스 150mm (0.01mm, 미쓰도요 500-196-30 또는 같은 급)</t>
+          <t>PTFE 그리스 (슈퍼루브) (85g)</t>
         </is>
       </c>
       <c r="E54" s="17" t="n">
-        <v>150000</v>
+        <v>9900</v>
       </c>
       <c r="F54" s="12" t="n">
         <v>1</v>
@@ -2469,11 +2469,11 @@
       </c>
       <c r="H54" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=미쓰도요 디지털 캘리퍼스 500-196-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="35" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/6071008034</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="24.9" customHeight="1" s="15">
       <c r="A55" s="16" t="n">
         <v>53</v>
       </c>
@@ -2489,11 +2489,11 @@
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>디지털 걸이 저울 (최대 10kg 이상, 5g 단위 이하)</t>
+          <t>나사 고정제 록타이트 243 (10ml)</t>
         </is>
       </c>
       <c r="E55" s="17" t="n">
-        <v>15000</v>
+        <v>8580</v>
       </c>
       <c r="F55" s="12" t="n">
         <v>1</v>
@@ -2504,11 +2504,11 @@
       </c>
       <c r="H55" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=디지털 걸이저울 10kg</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="35" customHeight="1" s="15">
+          <t>https://www.11st.co.kr/products/7426834008</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="24.9" customHeight="1" s="15">
       <c r="A56" s="16" t="n">
         <v>54</v>
       </c>
@@ -2524,11 +2524,11 @@
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>탁상 바이스 (조 폭 100mm (4인치), 작업대 고정)</t>
+          <t>열수축 튜브 세트 (1~14mm 164개)</t>
         </is>
       </c>
       <c r="E56" s="17" t="n">
-        <v>30000</v>
+        <v>750</v>
       </c>
       <c r="F56" s="12" t="n">
         <v>1</v>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="H56" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=탁상 바이스 4인치</t>
+          <t>https://www.coupang.com/vp/products/9183828751</t>
         </is>
       </c>
     </row>
@@ -2559,11 +2559,11 @@
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>철공용 평줄 (중목 250mm)</t>
+          <t>케이블 타이 (100개, 흑색)</t>
         </is>
       </c>
       <c r="E57" s="17" t="n">
-        <v>10000</v>
+        <v>770</v>
       </c>
       <c r="F57" s="12" t="n">
         <v>1</v>
@@ -2574,11 +2574,11 @@
       </c>
       <c r="H57" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=철공용 평줄 중목 250mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="24.9" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/8850608631</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="35" customHeight="1" s="15">
       <c r="A58" s="16" t="n">
         <v>56</v>
       </c>
@@ -2594,14 +2594,14 @@
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>철공용 평줄 (세목 200mm)</t>
+          <t>신호선 0.3SQ (약 22AWG) 10색 (10색 × 1m 세트)</t>
         </is>
       </c>
       <c r="E58" s="17" t="n">
-        <v>8000</v>
+        <v>1500</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G58" s="17">
         <f>F58*E58</f>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="H58" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=철공용 평줄 세목 200mm</t>
+          <t>https://www.coupang.com/vp/products/9183828539</t>
         </is>
       </c>
     </row>
@@ -2629,14 +2629,14 @@
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>앵글 그라인더 플랩 디스크 (4인치(100mm) #80)</t>
+          <t>디지털 캘리퍼스 미쓰도요 CD-15APX (150mm, 0.01mm (500-196-30 신형))</t>
         </is>
       </c>
       <c r="E59" s="17" t="n">
-        <v>2000</v>
+        <v>156400</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G59" s="17">
         <f>F59*E59</f>
@@ -2644,11 +2644,11 @@
       </c>
       <c r="H59" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=플랩디스크 4인치 80방</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="35" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/7773830124</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="24.9" customHeight="1" s="15">
       <c r="A60" s="16" t="n">
         <v>58</v>
       </c>
@@ -2664,14 +2664,14 @@
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>앵글 그라인더 절단석 (4인치(100mm) 두께 1mm)</t>
+          <t>디지털 걸이 저울 레쿠 (50kg × 10g)</t>
         </is>
       </c>
       <c r="E60" s="17" t="n">
-        <v>1000</v>
+        <v>25300</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G60" s="17">
         <f>F60*E60</f>
@@ -2679,11 +2679,11 @@
       </c>
       <c r="H60" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=절단석 4인치 1mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="24.9" customHeight="1" s="15">
+          <t>https://www.coupang.com/np/products/brand-shop?brandName=레쿠</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="35" customHeight="1" s="15">
       <c r="A61" s="16" t="n">
         <v>59</v>
       </c>
@@ -2699,14 +2699,14 @@
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>보안경 (투명, 측면 보호)</t>
+          <t>탁상 바이스 ITL (조 폭 100mm, 360도 회전)</t>
         </is>
       </c>
       <c r="E61" s="17" t="n">
-        <v>5000</v>
+        <v>34900</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G61" s="17">
         <f>F61*E61</f>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="H61" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=보안경 측면보호</t>
+          <t>https://www.coupang.com/vp/products/8992172012</t>
         </is>
       </c>
     </row>
@@ -2734,14 +2734,14 @@
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>절단 방지 장갑 (코팅)</t>
+          <t>철공용 평줄 중목 (250mm)</t>
         </is>
       </c>
       <c r="E62" s="17" t="n">
-        <v>3000</v>
+        <v>5800</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G62" s="17">
         <f>F62*E62</f>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="H62" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=절단방지 장갑</t>
+          <t>https://www.coupang.com/vp/products/8997744652</t>
         </is>
       </c>
     </row>
@@ -2769,11 +2769,11 @@
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>HSS 드릴 날 세트 (19개 (1~10mm))</t>
+          <t>철공용 평줄 세목 (200mm)</t>
         </is>
       </c>
       <c r="E63" s="17" t="n">
-        <v>7740</v>
+        <v>4600</v>
       </c>
       <c r="F63" s="12" t="n">
         <v>1</v>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="H63" s="12" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/2450926293</t>
+          <t>https://www.coupang.com/vp/products/8997744821</t>
         </is>
       </c>
     </row>
@@ -2804,14 +2804,14 @@
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>C클램프 (4인치(100mm))</t>
+          <t>플랩 디스크 100mm #80 (10개 봉)</t>
         </is>
       </c>
       <c r="E64" s="17" t="n">
-        <v>8000</v>
+        <v>7500</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G64" s="17">
         <f>F64*E64</f>
@@ -2819,11 +2819,11 @@
       </c>
       <c r="H64" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=C클램프 4인치</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="35" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/9416862249</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="24.9" customHeight="1" s="15">
       <c r="A65" s="16" t="n">
         <v>63</v>
       </c>
@@ -2839,14 +2839,14 @@
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>아두이노 레오나르도 R3 + USB 케이블 (ATmega32u4)</t>
+          <t>절단석 105mm 두께 1mm (5개 봉)</t>
         </is>
       </c>
       <c r="E65" s="17" t="n">
-        <v>9200</v>
+        <v>4000</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G65" s="17">
         <f>F65*E65</f>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="H65" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/1119152790</t>
+          <t>https://www.coupang.com/vp/products/9375758010</t>
         </is>
       </c>
     </row>
@@ -2874,14 +2874,14 @@
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>홀센서 A3144 (3핀)</t>
+          <t>보안경 (측면 보호) (투명)</t>
         </is>
       </c>
       <c r="E66" s="17" t="n">
-        <v>90</v>
+        <v>6290</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G66" s="17">
         <f>F66*E66</f>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="H66" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8520223332</t>
+          <t>https://www.coupang.com/vp/products/8800840444</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>네오디뮴 자석 (Ø6×3, 40개)</t>
+          <t>절단 방지 장갑 NBR 코팅 (L, 2개 묶음)</t>
         </is>
       </c>
       <c r="E67" s="17" t="n">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="H67" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/7119515778</t>
+          <t>https://www.coupang.com/vp/products/7759646279</t>
         </is>
       </c>
     </row>
@@ -2944,14 +2944,14 @@
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>가변저항 B10K (WH148 등 16mm) (D축 Ø6 15mm, 부싱 M7, 3핀)</t>
+          <t>HSS 드릴 날 세트 (19개 (1~10mm, 0.5 단위))</t>
         </is>
       </c>
       <c r="E68" s="17" t="n">
-        <v>2000</v>
+        <v>7740</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G68" s="17">
         <f>F68*E68</f>
@@ -2959,11 +2959,11 @@
       </c>
       <c r="H68" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=가변저항 B10K 16mm D축 15mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="24.9" customHeight="1" s="15">
+          <t>https://www.11st.co.kr/products/2450926293</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="35" customHeight="1" s="15">
       <c r="A69" s="16" t="n">
         <v>67</v>
       </c>
@@ -2979,14 +2979,14 @@
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>마이크로스위치 KW-11-3Z (레버형)</t>
+          <t>C클램프 4인치 (최대 벌림 105mm, 2개 묶음)</t>
         </is>
       </c>
       <c r="E69" s="17" t="n">
-        <v>400</v>
+        <v>10490</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G69" s="17">
         <f>F69*E69</f>
@@ -2994,11 +2994,11 @@
       </c>
       <c r="H69" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9167678186</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="24.9" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/8261073812</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="35" customHeight="1" s="15">
       <c r="A70" s="16" t="n">
         <v>68</v>
       </c>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>점퍼 케이블 M-F (40P 40cm)</t>
+          <t>아두이노 레오나르도 R3 + USB 케이블 (ATmega32u4)</t>
         </is>
       </c>
       <c r="E70" s="17" t="n">
-        <v>5300</v>
+        <v>9200</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G70" s="17">
         <f>F70*E70</f>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="H70" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9699042565</t>
+          <t>https://www.coupang.com/vp/products/1119152790</t>
         </is>
       </c>
     </row>
@@ -3049,14 +3049,14 @@
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>만능기판 (양면, 묶음)</t>
+          <t>홀센서 A3144 (3핀)</t>
         </is>
       </c>
       <c r="E71" s="17" t="n">
-        <v>15000</v>
+        <v>90</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G71" s="17">
         <f>F71*E71</f>
@@ -3064,11 +3064,11 @@
       </c>
       <c r="H71" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9661304796</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="35" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/8520223332</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="24.9" customHeight="1" s="15">
       <c r="A72" s="16" t="n">
         <v>70</v>
       </c>
@@ -3084,14 +3084,14 @@
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>자동차 릴레이 12V 40A + 소켓 (4핀, 배선된 소켓)</t>
+          <t>네오디뮴 자석 (Ø6×3, 40개)</t>
         </is>
       </c>
       <c r="E72" s="17" t="n">
-        <v>3100</v>
+        <v>11300</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G72" s="17">
         <f>F72*E72</f>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="H72" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6667848502</t>
+          <t>https://www.coupang.com/vp/products/7119515778</t>
         </is>
       </c>
     </row>
@@ -3119,14 +3119,14 @@
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>블레이드 퓨즈 + 인라인 홀더 세트 (15A 포함, 홀더 4 + 퓨즈 12)</t>
+          <t>가변저항 10K WH148 톱니 축 (16mm, 축 15mm, 부싱 M7, 3핀)</t>
         </is>
       </c>
       <c r="E73" s="17" t="n">
-        <v>8900</v>
+        <v>240</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G73" s="17">
         <f>F73*E73</f>
@@ -3134,11 +3134,11 @@
       </c>
       <c r="H73" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9663070188</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="35" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/8718871111</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="24.9" customHeight="1" s="15">
       <c r="A74" s="16" t="n">
         <v>72</v>
       </c>
@@ -3154,14 +3154,14 @@
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>비상정지 스위치 22mm (버섯형, 1a1b, 명판 포함 (A20B-V4E11R))</t>
+          <t>마이크로스위치 KW-11-3Z (레버형)</t>
         </is>
       </c>
       <c r="E74" s="17" t="n">
-        <v>15400</v>
+        <v>400</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G74" s="17">
         <f>F74*E74</f>
@@ -3169,11 +3169,11 @@
       </c>
       <c r="H74" s="12" t="inlineStr">
         <is>
-          <t>https://m.gmarket.co.kr/vi/product/711140155</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="35" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/9167678186</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="24.9" customHeight="1" s="15">
       <c r="A75" s="16" t="n">
         <v>73</v>
       </c>
@@ -3189,11 +3189,11 @@
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>비상정지 스위치 박스 (1구 (22mm 구멍))</t>
+          <t>점퍼 케이블 F-M (40P 40cm)</t>
         </is>
       </c>
       <c r="E75" s="17" t="n">
-        <v>13200</v>
+        <v>1300</v>
       </c>
       <c r="F75" s="12" t="n">
         <v>1</v>
@@ -3204,11 +3204,11 @@
       </c>
       <c r="H75" s="12" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/8521960628</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="24.9" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/9183828363</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="35" customHeight="1" s="15">
       <c r="A76" s="16" t="n">
         <v>74</v>
       </c>
@@ -3224,11 +3224,11 @@
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>5V 릴레이 모듈 1채널 (DM106)</t>
+          <t>만능기판 양면 2.54 (28×43홀 (약 71×109mm))</t>
         </is>
       </c>
       <c r="E76" s="17" t="n">
-        <v>2000</v>
+        <v>2700</v>
       </c>
       <c r="F76" s="12" t="n">
         <v>2</v>
@@ -3239,11 +3239,11 @@
       </c>
       <c r="H76" s="12" t="inlineStr">
         <is>
-          <t>https://item.gmarket.co.kr/Item?goodscode=1577801859</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="24.9" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/9181560693</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="35" customHeight="1" s="15">
       <c r="A77" s="16" t="n">
         <v>75</v>
       </c>
@@ -3259,14 +3259,14 @@
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>다이오드 1N4007 (10개)</t>
+          <t>자동차 릴레이 12V 40A + 소켓 (4핀, 배선된 소켓)</t>
         </is>
       </c>
       <c r="E77" s="17" t="n">
-        <v>700</v>
+        <v>3100</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G77" s="17">
         <f>F77*E77</f>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="H77" s="12" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/1453536560</t>
+          <t>https://www.coupang.com/vp/products/6667848502</t>
         </is>
       </c>
     </row>
@@ -3294,11 +3294,11 @@
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>저항 세트 1/4W (30종 × 20개 (10kΩ·4.7kΩ 포함))</t>
+          <t>블레이드 퓨즈 + 인라인 홀더 세트 (15A 포함, 홀더 4 + 퓨즈 12)</t>
         </is>
       </c>
       <c r="E78" s="17" t="n">
-        <v>4300</v>
+        <v>8900</v>
       </c>
       <c r="F78" s="12" t="n">
         <v>1</v>
@@ -3309,11 +3309,11 @@
       </c>
       <c r="H78" s="12" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/1969785917</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="24.9" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/9663070188</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="35" customHeight="1" s="15">
       <c r="A79" s="16" t="n">
         <v>77</v>
       </c>
@@ -3329,14 +3329,14 @@
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>실리콘 전선 16AWG 빨강·검정 (1m 세트)</t>
+          <t>비상정지 스위치 22mm + 1구 박스 (LAS0-K-11TSA, 1a1b)</t>
         </is>
       </c>
       <c r="E79" s="17" t="n">
-        <v>1310</v>
+        <v>18300</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G79" s="17">
         <f>F79*E79</f>
@@ -3344,11 +3344,11 @@
       </c>
       <c r="H79" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/7225302003</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="35" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/9169916764</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="24.9" customHeight="1" s="15">
       <c r="A80" s="16" t="n">
         <v>78</v>
       </c>
@@ -3364,14 +3364,14 @@
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>절연 암 평형 단자 250 (6.3mm) (22~16AWG, 2개 봉)</t>
+          <t>5V 릴레이 모듈 1채널 KY-019 (1채널)</t>
         </is>
       </c>
       <c r="E80" s="17" t="n">
-        <v>310</v>
+        <v>550</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G80" s="17">
         <f>F80*E80</f>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="H80" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8667960491</t>
+          <t>https://www.coupang.com/vp/products/9162331915</t>
         </is>
       </c>
     </row>
@@ -3399,11 +3399,11 @@
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>배송비 (판매처별 합계)</t>
+          <t>다이오드 1N4007 (10개)</t>
         </is>
       </c>
       <c r="E81" s="17" t="n">
-        <v>140000</v>
+        <v>690</v>
       </c>
       <c r="F81" s="12" t="n">
         <v>1</v>
@@ -3414,35 +3414,205 @@
       </c>
       <c r="H81" s="12" t="inlineStr">
         <is>
+          <t>https://www.coupang.com/vp/products/9705767581</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="24.9" customHeight="1" s="15">
+      <c r="A82" s="16" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" s="12" t="inlineStr">
+        <is>
+          <t>RPM</t>
+        </is>
+      </c>
+      <c r="C82" s="12" t="inlineStr">
+        <is>
+          <t>홍경표, 장수빈</t>
+        </is>
+      </c>
+      <c r="D82" s="12" t="inlineStr">
+        <is>
+          <t>저항 1/4W 10kΩ (10개)</t>
+        </is>
+      </c>
+      <c r="E82" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="F82" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="17">
+        <f>F82*E82</f>
+        <v/>
+      </c>
+      <c r="H82" s="12" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9701925630</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="24.9" customHeight="1" s="15">
+      <c r="A83" s="16" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" s="12" t="inlineStr">
+        <is>
+          <t>RPM</t>
+        </is>
+      </c>
+      <c r="C83" s="12" t="inlineStr">
+        <is>
+          <t>홍경표, 장수빈</t>
+        </is>
+      </c>
+      <c r="D83" s="12" t="inlineStr">
+        <is>
+          <t>저항 1/4W 4.7kΩ (10개)</t>
+        </is>
+      </c>
+      <c r="E83" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="F83" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="17">
+        <f>F83*E83</f>
+        <v/>
+      </c>
+      <c r="H83" s="12" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9701925630</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="24.9" customHeight="1" s="15">
+      <c r="A84" s="16" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" s="12" t="inlineStr">
+        <is>
+          <t>RPM</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="inlineStr">
+        <is>
+          <t>홍경표, 장수빈</t>
+        </is>
+      </c>
+      <c r="D84" s="12" t="inlineStr">
+        <is>
+          <t>실리콘 전선 16AWG 빨강·검정 (1m 세트)</t>
+        </is>
+      </c>
+      <c r="E84" s="17" t="n">
+        <v>1310</v>
+      </c>
+      <c r="F84" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G84" s="17">
+        <f>F84*E84</f>
+        <v/>
+      </c>
+      <c r="H84" s="12" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7225302003</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="35" customHeight="1" s="15">
+      <c r="A85" s="16" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" s="12" t="inlineStr">
+        <is>
+          <t>RPM</t>
+        </is>
+      </c>
+      <c r="C85" s="12" t="inlineStr">
+        <is>
+          <t>홍경표, 장수빈</t>
+        </is>
+      </c>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t>절연 암 평형 단자 250 (6.3mm) (10개 봉)</t>
+        </is>
+      </c>
+      <c r="E85" s="17" t="n">
+        <v>800</v>
+      </c>
+      <c r="F85" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="17">
+        <f>F85*E85</f>
+        <v/>
+      </c>
+      <c r="H85" s="12" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9181548711</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="24.9" customHeight="1" s="15">
+      <c r="A86" s="16" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" s="12" t="inlineStr">
+        <is>
+          <t>RPM</t>
+        </is>
+      </c>
+      <c r="C86" s="12" t="inlineStr">
+        <is>
+          <t>홍경표, 장수빈</t>
+        </is>
+      </c>
+      <c r="D86" s="12" t="inlineStr">
+        <is>
+          <t>배송비 (판매처별 합계)</t>
+        </is>
+      </c>
+      <c r="E86" s="17" t="n">
+        <v>57800</v>
+      </c>
+      <c r="F86" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="17">
+        <f>F86*E86</f>
+        <v/>
+      </c>
+      <c r="H86" s="12" t="inlineStr">
+        <is>
           <t>판매처별 배송비 합계</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="9" t="n"/>
-      <c r="B82" s="6" t="n"/>
-      <c r="C82" s="6" t="n"/>
-      <c r="D82" s="6" t="n"/>
-      <c r="E82" s="18" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="9" t="n"/>
+      <c r="B87" s="6" t="n"/>
+      <c r="C87" s="6" t="n"/>
+      <c r="D87" s="6" t="n"/>
+      <c r="E87" s="18" t="inlineStr">
         <is>
           <t>소계</t>
         </is>
       </c>
-      <c r="F82" s="19">
-        <f>SUM(F3:F81)</f>
-        <v/>
-      </c>
-      <c r="G82" s="20">
-        <f>SUM(G3:G81)</f>
-        <v/>
-      </c>
-      <c r="H82" s="6" t="n"/>
-    </row>
-    <row r="83" s="15"/>
-    <row r="84" s="15"/>
-    <row r="85" s="15"/>
-    <row r="86" s="15"/>
-    <row r="87" s="15"/>
+      <c r="F87" s="19">
+        <f>SUM(F3:F86)</f>
+        <v/>
+      </c>
+      <c r="G87" s="20">
+        <f>SUM(G3:G86)</f>
+        <v/>
+      </c>
+      <c r="H87" s="6" t="n"/>
+    </row>
     <row r="88" s="15"/>
     <row r="89" s="15"/>
     <row r="90" s="15"/>
@@ -3457,6 +3627,11 @@
     <row r="99" s="15"/>
     <row r="100" s="15"/>
     <row r="101" s="15"/>
+    <row r="102" s="15"/>
+    <row r="103" s="15"/>
+    <row r="104" s="15"/>
+    <row r="105" s="15"/>
+    <row r="106" s="15"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
@@ -3540,6 +3715,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId83"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/v4/창체_물품계획서_RPM.xlsx
+++ b/v4/창체_물품계획서_RPM.xlsx
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="6.5" customWidth="1" style="10" min="1" max="1"/>
@@ -669,14 +669,14 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>볼 베어링 6001ZZ NSK (12×28×8)</t>
+          <t>볼 베어링 6001ZZ (12×28×8, 10개 묶음)</t>
         </is>
       </c>
       <c r="E3" s="17" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="F3" s="12" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="G3" s="17">
         <f>F3*E3</f>
@@ -684,7 +684,7 @@
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/1432577678</t>
+          <t>https://www.coupang.com/vp/products/8630678241</t>
         </is>
       </c>
     </row>
@@ -704,11 +704,11 @@
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>볼 베어링 6003ZZ NSK (17×35×10)</t>
+          <t>볼 베어링 6003ZZ (17×35×10)</t>
         </is>
       </c>
       <c r="E4" s="17" t="n">
-        <v>4000</v>
+        <v>1100</v>
       </c>
       <c r="F4" s="12" t="n">
         <v>2</v>
@@ -719,7 +719,7 @@
       </c>
       <c r="H4" s="12" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/1432577678</t>
+          <t>https://www.coupang.com/vp/products/8230435105</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
         <v>1500</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G13" s="17">
         <f>F13*E13</f>
@@ -2069,14 +2069,14 @@
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>PLA 필라멘트 울티메이커 정품 검정 (2.85mm, 750g)</t>
+          <t>PLA 필라멘트 2.85mm 1kg 검정 (2.85mm, 1kg)</t>
         </is>
       </c>
       <c r="E43" s="17" t="n">
-        <v>75900</v>
+        <v>35000</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G43" s="17">
         <f>F43*E43</f>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9783043879</t>
+          <t>https://www.coupang.com/np/search?q=PLA 필라멘트 2.85mm 1kg</t>
         </is>
       </c>
     </row>
@@ -2104,11 +2104,11 @@
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>PLA 필라멘트 울티메이커 정품 주황 (2.85mm, 750g)</t>
+          <t>PLA 필라멘트 2.85mm 1kg 주황 (2.85mm, 1kg)</t>
         </is>
       </c>
       <c r="E44" s="17" t="n">
-        <v>75900</v>
+        <v>35000</v>
       </c>
       <c r="F44" s="12" t="n">
         <v>2</v>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9783044238</t>
+          <t>https://www.coupang.com/np/search?q=PLA 필라멘트 2.85mm 1kg</t>
         </is>
       </c>
     </row>
@@ -2139,14 +2139,14 @@
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>PLA 필라멘트 울티메이커 정품 파랑 (2.85mm, 750g)</t>
+          <t>PLA 필라멘트 2.85mm 1kg 파랑 (2.85mm, 1kg)</t>
         </is>
       </c>
       <c r="E45" s="17" t="n">
-        <v>75900</v>
+        <v>35000</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G45" s="17">
         <f>F45*E45</f>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="H45" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9783043880</t>
+          <t>https://www.coupang.com/np/search?q=PLA 필라멘트 2.85mm 1kg</t>
         </is>
       </c>
     </row>
@@ -2174,11 +2174,11 @@
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>PLA 필라멘트 울티메이커 정품 노랑 (2.85mm, 750g)</t>
+          <t>2액형 에폭시 접착제 (주사기형 25ml, 2개 묶음)</t>
         </is>
       </c>
       <c r="E46" s="17" t="n">
-        <v>75900</v>
+        <v>7650</v>
       </c>
       <c r="F46" s="12" t="n">
         <v>1</v>
@@ -2189,11 +2189,11 @@
       </c>
       <c r="H46" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9783043850</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="35" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/2725054</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="24.9" customHeight="1" s="15">
       <c r="A47" s="16" t="n">
         <v>45</v>
       </c>
@@ -2209,11 +2209,11 @@
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>2액형 에폭시 접착제 (주사기형 25ml, 2개 묶음)</t>
+          <t>순간접착제 (젤 타입 2개)</t>
         </is>
       </c>
       <c r="E47" s="17" t="n">
-        <v>7650</v>
+        <v>3000</v>
       </c>
       <c r="F47" s="12" t="n">
         <v>1</v>
@@ -2224,11 +2224,11 @@
       </c>
       <c r="H47" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/2725054</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="24.9" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/8643897709</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="35" customHeight="1" s="15">
       <c r="A48" s="16" t="n">
         <v>46</v>
       </c>
@@ -2244,11 +2244,11 @@
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>순간접착제 (젤 타입 2개)</t>
+          <t>자전거 브레이크 케이블 세트 (속선 2 + 아우터 + 끝 캡)</t>
         </is>
       </c>
       <c r="E48" s="17" t="n">
-        <v>3000</v>
+        <v>6900</v>
       </c>
       <c r="F48" s="12" t="n">
         <v>1</v>
@@ -2259,11 +2259,11 @@
       </c>
       <c r="H48" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8643897709</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="35" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/8305908512</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="24.9" customHeight="1" s="15">
       <c r="A49" s="16" t="n">
         <v>47</v>
       </c>
@@ -2279,11 +2279,11 @@
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>자전거 브레이크 케이블 세트 (속선 2 + 아우터 + 끝 캡)</t>
+          <t>MDF 판 (12T 300×1200 재단)</t>
         </is>
       </c>
       <c r="E49" s="17" t="n">
-        <v>6900</v>
+        <v>9600</v>
       </c>
       <c r="F49" s="12" t="n">
         <v>1</v>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="H49" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8305908512</t>
+          <t>https://www.coupang.com/vp/products/71452005</t>
         </is>
       </c>
     </row>
@@ -2314,11 +2314,11 @@
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>MDF 판 (12T 300×1200 재단)</t>
+          <t>투명 아크릴 3T 치수 재단 (250×321)</t>
         </is>
       </c>
       <c r="E50" s="17" t="n">
-        <v>9600</v>
+        <v>6000</v>
       </c>
       <c r="F50" s="12" t="n">
         <v>1</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="H50" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/71452005</t>
+          <t>https://www.11st.co.kr/products/4918717495</t>
         </is>
       </c>
     </row>
@@ -2349,14 +2349,14 @@
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>투명 아크릴 3T 치수 재단 (250×321)</t>
+          <t>투명 아크릴 3T 치수 재단 (200×321)</t>
         </is>
       </c>
       <c r="E51" s="17" t="n">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G51" s="17">
         <f>F51*E51</f>
@@ -2384,14 +2384,14 @@
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>투명 아크릴 3T 치수 재단 (200×321)</t>
+          <t>PTFE 그리스 (슈퍼루브) (85g)</t>
         </is>
       </c>
       <c r="E52" s="17" t="n">
-        <v>5000</v>
+        <v>9900</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G52" s="17">
         <f>F52*E52</f>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="H52" s="12" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/4918717495</t>
+          <t>https://www.coupang.com/vp/products/6071008034</t>
         </is>
       </c>
     </row>
@@ -2419,11 +2419,11 @@
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>투명 아크릴 A3 3T (여분) (297×420)</t>
+          <t>나사 고정제 록타이트 243 (10ml)</t>
         </is>
       </c>
       <c r="E53" s="17" t="n">
-        <v>9000</v>
+        <v>8580</v>
       </c>
       <c r="F53" s="12" t="n">
         <v>1</v>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="H53" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9593337115</t>
+          <t>https://www.11st.co.kr/products/7426834008</t>
         </is>
       </c>
     </row>
@@ -2454,11 +2454,11 @@
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>PTFE 그리스 (슈퍼루브) (85g)</t>
+          <t>열수축 튜브 세트 (1~14mm 164개)</t>
         </is>
       </c>
       <c r="E54" s="17" t="n">
-        <v>9900</v>
+        <v>750</v>
       </c>
       <c r="F54" s="12" t="n">
         <v>1</v>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="H54" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6071008034</t>
+          <t>https://www.coupang.com/vp/products/9183828751</t>
         </is>
       </c>
     </row>
@@ -2489,11 +2489,11 @@
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>나사 고정제 록타이트 243 (10ml)</t>
+          <t>케이블 타이 (100개, 흑색)</t>
         </is>
       </c>
       <c r="E55" s="17" t="n">
-        <v>8580</v>
+        <v>770</v>
       </c>
       <c r="F55" s="12" t="n">
         <v>1</v>
@@ -2504,11 +2504,11 @@
       </c>
       <c r="H55" s="12" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/7426834008</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="24.9" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/8850608631</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="35" customHeight="1" s="15">
       <c r="A56" s="16" t="n">
         <v>54</v>
       </c>
@@ -2524,14 +2524,14 @@
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>열수축 튜브 세트 (1~14mm 164개)</t>
+          <t>신호선 0.3SQ (약 22AWG) 10색 (10색 × 1m 세트)</t>
         </is>
       </c>
       <c r="E56" s="17" t="n">
-        <v>750</v>
+        <v>1500</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G56" s="17">
         <f>F56*E56</f>
@@ -2539,11 +2539,11 @@
       </c>
       <c r="H56" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9183828751</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="24.9" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/9183828539</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="35" customHeight="1" s="15">
       <c r="A57" s="16" t="n">
         <v>55</v>
       </c>
@@ -2559,11 +2559,11 @@
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>케이블 타이 (100개, 흑색)</t>
+          <t>디지털 캘리퍼스 (150mm, 분해능 0.01mm)</t>
         </is>
       </c>
       <c r="E57" s="17" t="n">
-        <v>770</v>
+        <v>20000</v>
       </c>
       <c r="F57" s="12" t="n">
         <v>1</v>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="H57" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8850608631</t>
+          <t>https://www.coupang.com/np/search?q=디지털 캘리퍼스 150mm</t>
         </is>
       </c>
     </row>
@@ -2594,14 +2594,14 @@
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>신호선 0.3SQ (약 22AWG) 10색 (10색 × 1m 세트)</t>
+          <t>탁상 바이스 (조 폭 75~100mm, 책상에 클램프 고정)</t>
         </is>
       </c>
       <c r="E58" s="17" t="n">
-        <v>1500</v>
+        <v>20000</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G58" s="17">
         <f>F58*E58</f>
@@ -2609,11 +2609,11 @@
       </c>
       <c r="H58" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9183828539</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="35" customHeight="1" s="15">
+          <t>https://www.coupang.com/np/search?q=탁상 바이스</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="24.9" customHeight="1" s="15">
       <c r="A59" s="16" t="n">
         <v>57</v>
       </c>
@@ -2629,11 +2629,11 @@
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>디지털 캘리퍼스 미쓰도요 CD-15APX (150mm, 0.01mm (500-196-30 신형))</t>
+          <t>철공용 평줄 중목 (250mm)</t>
         </is>
       </c>
       <c r="E59" s="17" t="n">
-        <v>156400</v>
+        <v>5800</v>
       </c>
       <c r="F59" s="12" t="n">
         <v>1</v>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="H59" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/7773830124</t>
+          <t>https://www.coupang.com/vp/products/8997744652</t>
         </is>
       </c>
     </row>
@@ -2664,11 +2664,11 @@
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>디지털 걸이 저울 레쿠 (50kg × 10g)</t>
+          <t>철공용 평줄 세목 (200mm)</t>
         </is>
       </c>
       <c r="E60" s="17" t="n">
-        <v>25300</v>
+        <v>4600</v>
       </c>
       <c r="F60" s="12" t="n">
         <v>1</v>
@@ -2679,11 +2679,11 @@
       </c>
       <c r="H60" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/products/brand-shop?brandName=레쿠</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="35" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/8997744821</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="24.9" customHeight="1" s="15">
       <c r="A61" s="16" t="n">
         <v>59</v>
       </c>
@@ -2699,11 +2699,11 @@
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>탁상 바이스 ITL (조 폭 100mm, 360도 회전)</t>
+          <t>플랩 디스크 100mm #80 (10개 봉)</t>
         </is>
       </c>
       <c r="E61" s="17" t="n">
-        <v>34900</v>
+        <v>7500</v>
       </c>
       <c r="F61" s="12" t="n">
         <v>1</v>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="H61" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8992172012</t>
+          <t>https://www.coupang.com/vp/products/9416862249</t>
         </is>
       </c>
     </row>
@@ -2734,11 +2734,11 @@
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>철공용 평줄 중목 (250mm)</t>
+          <t>절단석 105mm 두께 1mm (5개 봉)</t>
         </is>
       </c>
       <c r="E62" s="17" t="n">
-        <v>5800</v>
+        <v>4000</v>
       </c>
       <c r="F62" s="12" t="n">
         <v>1</v>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="H62" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8997744652</t>
+          <t>https://www.coupang.com/vp/products/9375758010</t>
         </is>
       </c>
     </row>
@@ -2769,11 +2769,11 @@
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>철공용 평줄 세목 (200mm)</t>
+          <t>보안경 (측면 보호) (투명)</t>
         </is>
       </c>
       <c r="E63" s="17" t="n">
-        <v>4600</v>
+        <v>6290</v>
       </c>
       <c r="F63" s="12" t="n">
         <v>1</v>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="H63" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8997744821</t>
+          <t>https://www.coupang.com/vp/products/8800840444</t>
         </is>
       </c>
     </row>
@@ -2804,11 +2804,11 @@
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>플랩 디스크 100mm #80 (10개 봉)</t>
+          <t>NBR 코팅 장갑 (L)</t>
         </is>
       </c>
       <c r="E64" s="17" t="n">
-        <v>7500</v>
+        <v>3000</v>
       </c>
       <c r="F64" s="12" t="n">
         <v>1</v>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="H64" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9416862249</t>
+          <t>https://www.coupang.com/np/search?q=NBR 코팅장갑</t>
         </is>
       </c>
     </row>
@@ -2839,11 +2839,11 @@
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>절단석 105mm 두께 1mm (5개 봉)</t>
+          <t>HSS 드릴 날 2.5mm (1개)</t>
         </is>
       </c>
       <c r="E65" s="17" t="n">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="F65" s="12" t="n">
         <v>1</v>
@@ -2854,11 +2854,11 @@
       </c>
       <c r="H65" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9375758010</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="24.9" customHeight="1" s="15">
+          <t>https://www.coupang.com/np/search?q=HSS 드릴날 2.5mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="35" customHeight="1" s="15">
       <c r="A66" s="16" t="n">
         <v>64</v>
       </c>
@@ -2874,14 +2874,14 @@
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>보안경 (측면 보호) (투명)</t>
+          <t>C클램프 4인치 (최대 벌림 105mm, 2개 묶음)</t>
         </is>
       </c>
       <c r="E66" s="17" t="n">
-        <v>6290</v>
+        <v>10490</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G66" s="17">
         <f>F66*E66</f>
@@ -2889,11 +2889,11 @@
       </c>
       <c r="H66" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8800840444</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="24.9" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/8261073812</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="35" customHeight="1" s="15">
       <c r="A67" s="16" t="n">
         <v>65</v>
       </c>
@@ -2909,11 +2909,11 @@
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>절단 방지 장갑 NBR 코팅 (L, 2개 묶음)</t>
+          <t>아두이노 레오나르도 R3 + USB 케이블 (ATmega32u4)</t>
         </is>
       </c>
       <c r="E67" s="17" t="n">
-        <v>11300</v>
+        <v>9200</v>
       </c>
       <c r="F67" s="12" t="n">
         <v>1</v>
@@ -2924,11 +2924,11 @@
       </c>
       <c r="H67" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/7759646279</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="35" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/1119152790</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="24.9" customHeight="1" s="15">
       <c r="A68" s="16" t="n">
         <v>66</v>
       </c>
@@ -2944,14 +2944,14 @@
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>HSS 드릴 날 세트 (19개 (1~10mm, 0.5 단위))</t>
+          <t>홀센서 A3144 (3핀)</t>
         </is>
       </c>
       <c r="E68" s="17" t="n">
-        <v>7740</v>
+        <v>90</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G68" s="17">
         <f>F68*E68</f>
@@ -2959,11 +2959,11 @@
       </c>
       <c r="H68" s="12" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/2450926293</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="35" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/8520223332</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="24.9" customHeight="1" s="15">
       <c r="A69" s="16" t="n">
         <v>67</v>
       </c>
@@ -2979,11 +2979,11 @@
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>C클램프 4인치 (최대 벌림 105mm, 2개 묶음)</t>
+          <t>네오디뮴 자석 (Ø6×3, 40개)</t>
         </is>
       </c>
       <c r="E69" s="17" t="n">
-        <v>10490</v>
+        <v>11300</v>
       </c>
       <c r="F69" s="12" t="n">
         <v>1</v>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="H69" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8261073812</t>
+          <t>https://www.coupang.com/vp/products/7119515778</t>
         </is>
       </c>
     </row>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>아두이노 레오나르도 R3 + USB 케이블 (ATmega32u4)</t>
+          <t>가변저항 10K WH148 톱니 축 (16mm, 축 15mm, 부싱 M7, 3핀)</t>
         </is>
       </c>
       <c r="E70" s="17" t="n">
-        <v>9200</v>
+        <v>240</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G70" s="17">
         <f>F70*E70</f>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="H70" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/1119152790</t>
+          <t>https://www.coupang.com/vp/products/8718871111</t>
         </is>
       </c>
     </row>
@@ -3049,14 +3049,14 @@
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>홀센서 A3144 (3핀)</t>
+          <t>마이크로스위치 KW-11-3Z (레버형)</t>
         </is>
       </c>
       <c r="E71" s="17" t="n">
-        <v>90</v>
+        <v>400</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G71" s="17">
         <f>F71*E71</f>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="H71" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8520223332</t>
+          <t>https://www.coupang.com/vp/products/9167678186</t>
         </is>
       </c>
     </row>
@@ -3084,11 +3084,11 @@
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>네오디뮴 자석 (Ø6×3, 40개)</t>
+          <t>점퍼 케이블 F-M (40P 40cm)</t>
         </is>
       </c>
       <c r="E72" s="17" t="n">
-        <v>11300</v>
+        <v>1300</v>
       </c>
       <c r="F72" s="12" t="n">
         <v>1</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="H72" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/7119515778</t>
+          <t>https://www.coupang.com/vp/products/9183828363</t>
         </is>
       </c>
     </row>
@@ -3119,14 +3119,14 @@
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>가변저항 10K WH148 톱니 축 (16mm, 축 15mm, 부싱 M7, 3핀)</t>
+          <t>만능기판 양면 2.54 (28×43홀 (약 71×109mm))</t>
         </is>
       </c>
       <c r="E73" s="17" t="n">
-        <v>240</v>
+        <v>2700</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G73" s="17">
         <f>F73*E73</f>
@@ -3134,11 +3134,11 @@
       </c>
       <c r="H73" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8718871111</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="24.9" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/9181560693</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="35" customHeight="1" s="15">
       <c r="A74" s="16" t="n">
         <v>72</v>
       </c>
@@ -3154,14 +3154,14 @@
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>마이크로스위치 KW-11-3Z (레버형)</t>
+          <t>자동차 릴레이 12V 40A + 소켓 (4핀, 배선된 소켓)</t>
         </is>
       </c>
       <c r="E74" s="17" t="n">
-        <v>400</v>
+        <v>3100</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G74" s="17">
         <f>F74*E74</f>
@@ -3169,11 +3169,11 @@
       </c>
       <c r="H74" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9167678186</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="24.9" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/6667848502</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="35" customHeight="1" s="15">
       <c r="A75" s="16" t="n">
         <v>73</v>
       </c>
@@ -3189,11 +3189,11 @@
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>점퍼 케이블 F-M (40P 40cm)</t>
+          <t>블레이드 퓨즈 + 인라인 홀더 세트 (15A 포함, 홀더 4 + 퓨즈 12)</t>
         </is>
       </c>
       <c r="E75" s="17" t="n">
-        <v>1300</v>
+        <v>8900</v>
       </c>
       <c r="F75" s="12" t="n">
         <v>1</v>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="H75" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9183828363</t>
+          <t>https://www.coupang.com/vp/products/9663070188</t>
         </is>
       </c>
     </row>
@@ -3224,14 +3224,14 @@
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>만능기판 양면 2.54 (28×43홀 (약 71×109mm))</t>
+          <t>비상정지 스위치 22mm + 1구 박스 (LAS0-K-11TSA, 1a1b)</t>
         </is>
       </c>
       <c r="E76" s="17" t="n">
-        <v>2700</v>
+        <v>18300</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G76" s="17">
         <f>F76*E76</f>
@@ -3239,11 +3239,11 @@
       </c>
       <c r="H76" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9181560693</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="35" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/9169916764</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="24.9" customHeight="1" s="15">
       <c r="A77" s="16" t="n">
         <v>75</v>
       </c>
@@ -3259,14 +3259,14 @@
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>자동차 릴레이 12V 40A + 소켓 (4핀, 배선된 소켓)</t>
+          <t>5V 릴레이 모듈 1채널 KY-019 (1채널)</t>
         </is>
       </c>
       <c r="E77" s="17" t="n">
-        <v>3100</v>
+        <v>550</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G77" s="17">
         <f>F77*E77</f>
@@ -3274,11 +3274,11 @@
       </c>
       <c r="H77" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6667848502</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="35" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/9162331915</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="24.9" customHeight="1" s="15">
       <c r="A78" s="16" t="n">
         <v>76</v>
       </c>
@@ -3294,11 +3294,11 @@
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>블레이드 퓨즈 + 인라인 홀더 세트 (15A 포함, 홀더 4 + 퓨즈 12)</t>
+          <t>다이오드 1N4007 (10개)</t>
         </is>
       </c>
       <c r="E78" s="17" t="n">
-        <v>8900</v>
+        <v>690</v>
       </c>
       <c r="F78" s="12" t="n">
         <v>1</v>
@@ -3309,11 +3309,11 @@
       </c>
       <c r="H78" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9663070188</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="35" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/9705767581</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="24.9" customHeight="1" s="15">
       <c r="A79" s="16" t="n">
         <v>77</v>
       </c>
@@ -3329,11 +3329,11 @@
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>비상정지 스위치 22mm + 1구 박스 (LAS0-K-11TSA, 1a1b)</t>
+          <t>저항 1/4W 10kΩ (10개)</t>
         </is>
       </c>
       <c r="E79" s="17" t="n">
-        <v>18300</v>
+        <v>80</v>
       </c>
       <c r="F79" s="12" t="n">
         <v>1</v>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="H79" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9169916764</t>
+          <t>https://www.coupang.com/vp/products/9701925630</t>
         </is>
       </c>
     </row>
@@ -3364,14 +3364,14 @@
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>5V 릴레이 모듈 1채널 KY-019 (1채널)</t>
+          <t>저항 1/4W 4.7kΩ (10개)</t>
         </is>
       </c>
       <c r="E80" s="17" t="n">
-        <v>550</v>
+        <v>80</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G80" s="17">
         <f>F80*E80</f>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="H80" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9162331915</t>
+          <t>https://www.coupang.com/vp/products/9701925630</t>
         </is>
       </c>
     </row>
@@ -3399,14 +3399,14 @@
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>다이오드 1N4007 (10개)</t>
+          <t>실리콘 전선 16AWG 빨강·검정 (1m 세트)</t>
         </is>
       </c>
       <c r="E81" s="17" t="n">
-        <v>690</v>
+        <v>1310</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G81" s="17">
         <f>F81*E81</f>
@@ -3414,11 +3414,11 @@
       </c>
       <c r="H81" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9705767581</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="24.9" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/7225302003</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="35" customHeight="1" s="15">
       <c r="A82" s="16" t="n">
         <v>80</v>
       </c>
@@ -3434,11 +3434,11 @@
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>저항 1/4W 10kΩ (10개)</t>
+          <t>절연 암 평형 단자 250 (6.3mm) (10개 봉)</t>
         </is>
       </c>
       <c r="E82" s="17" t="n">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="F82" s="12" t="n">
         <v>1</v>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="H82" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9701925630</t>
+          <t>https://www.coupang.com/vp/products/9181548711</t>
         </is>
       </c>
     </row>
@@ -3469,11 +3469,11 @@
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>저항 1/4W 4.7kΩ (10개)</t>
+          <t>배송비 (판매처별 합계)</t>
         </is>
       </c>
       <c r="E83" s="17" t="n">
-        <v>80</v>
+        <v>57800</v>
       </c>
       <c r="F83" s="12" t="n">
         <v>1</v>
@@ -3484,135 +3484,33 @@
       </c>
       <c r="H83" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9701925630</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="24.9" customHeight="1" s="15">
-      <c r="A84" s="16" t="n">
-        <v>82</v>
-      </c>
-      <c r="B84" s="12" t="inlineStr">
-        <is>
-          <t>RPM</t>
-        </is>
-      </c>
-      <c r="C84" s="12" t="inlineStr">
-        <is>
-          <t>홍경표, 장수빈</t>
-        </is>
-      </c>
-      <c r="D84" s="12" t="inlineStr">
-        <is>
-          <t>실리콘 전선 16AWG 빨강·검정 (1m 세트)</t>
-        </is>
-      </c>
-      <c r="E84" s="17" t="n">
-        <v>1310</v>
-      </c>
-      <c r="F84" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="G84" s="17">
-        <f>F84*E84</f>
-        <v/>
-      </c>
-      <c r="H84" s="12" t="inlineStr">
-        <is>
-          <t>https://www.coupang.com/vp/products/7225302003</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="35" customHeight="1" s="15">
-      <c r="A85" s="16" t="n">
-        <v>83</v>
-      </c>
-      <c r="B85" s="12" t="inlineStr">
-        <is>
-          <t>RPM</t>
-        </is>
-      </c>
-      <c r="C85" s="12" t="inlineStr">
-        <is>
-          <t>홍경표, 장수빈</t>
-        </is>
-      </c>
-      <c r="D85" s="12" t="inlineStr">
-        <is>
-          <t>절연 암 평형 단자 250 (6.3mm) (10개 봉)</t>
-        </is>
-      </c>
-      <c r="E85" s="17" t="n">
-        <v>800</v>
-      </c>
-      <c r="F85" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" s="17">
-        <f>F85*E85</f>
-        <v/>
-      </c>
-      <c r="H85" s="12" t="inlineStr">
-        <is>
-          <t>https://www.coupang.com/vp/products/9181548711</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="24.9" customHeight="1" s="15">
-      <c r="A86" s="16" t="n">
-        <v>84</v>
-      </c>
-      <c r="B86" s="12" t="inlineStr">
-        <is>
-          <t>RPM</t>
-        </is>
-      </c>
-      <c r="C86" s="12" t="inlineStr">
-        <is>
-          <t>홍경표, 장수빈</t>
-        </is>
-      </c>
-      <c r="D86" s="12" t="inlineStr">
-        <is>
-          <t>배송비 (판매처별 합계)</t>
-        </is>
-      </c>
-      <c r="E86" s="17" t="n">
-        <v>57800</v>
-      </c>
-      <c r="F86" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G86" s="17">
-        <f>F86*E86</f>
-        <v/>
-      </c>
-      <c r="H86" s="12" t="inlineStr">
-        <is>
           <t>판매처별 배송비 합계</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="9" t="n"/>
-      <c r="B87" s="6" t="n"/>
-      <c r="C87" s="6" t="n"/>
-      <c r="D87" s="6" t="n"/>
-      <c r="E87" s="18" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="9" t="n"/>
+      <c r="B84" s="6" t="n"/>
+      <c r="C84" s="6" t="n"/>
+      <c r="D84" s="6" t="n"/>
+      <c r="E84" s="18" t="inlineStr">
         <is>
           <t>소계</t>
         </is>
       </c>
-      <c r="F87" s="19">
-        <f>SUM(F3:F86)</f>
-        <v/>
-      </c>
-      <c r="G87" s="20">
-        <f>SUM(G3:G86)</f>
-        <v/>
-      </c>
-      <c r="H87" s="6" t="n"/>
-    </row>
+      <c r="F84" s="19">
+        <f>SUM(F3:F83)</f>
+        <v/>
+      </c>
+      <c r="G84" s="20">
+        <f>SUM(G3:G83)</f>
+        <v/>
+      </c>
+      <c r="H84" s="6" t="n"/>
+    </row>
+    <row r="85" s="15"/>
+    <row r="86" s="15"/>
+    <row r="87" s="15"/>
     <row r="88" s="15"/>
     <row r="89" s="15"/>
     <row r="90" s="15"/>
@@ -3629,9 +3527,6 @@
     <row r="101" s="15"/>
     <row r="102" s="15"/>
     <row r="103" s="15"/>
-    <row r="104" s="15"/>
-    <row r="105" s="15"/>
-    <row r="106" s="15"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
@@ -3717,9 +3612,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId83"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/v4/창체_물품계획서_RPM.xlsx
+++ b/v4/창체_물품계획서_RPM.xlsx
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="6.5" customWidth="1" style="10" min="1" max="1"/>
@@ -704,7 +704,7 @@
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>볼 베어링 6003ZZ (17×35×10)</t>
+          <t>볼 베어링 6003ZZ KYK (17×35×10)</t>
         </is>
       </c>
       <c r="E4" s="17" t="n">
@@ -1019,14 +1019,14 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>샤프트 칼라 Ø6 (무두볼트 고정) (안 6 · 바깥 12 · 폭 6)</t>
+          <t>압축 스프링 SUS304 (C252 대신) (선경 1.5 · 외경 18 · 자유장 25)</t>
         </is>
       </c>
       <c r="E13" s="17" t="n">
-        <v>1500</v>
+        <v>1590</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G13" s="17">
         <f>F13*E13</f>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>https://item.gmarket.co.kr/Item?goodscode=4101441390</t>
+          <t>https://www.coupang.com/vp/products/4387963066</t>
         </is>
       </c>
     </row>
@@ -1054,14 +1054,14 @@
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>압축 스프링 SUS304 (C252 대신) (선경 1.5 · 외경 18 · 자유장 25)</t>
+          <t>압축 스프링 SUS304 (C147 대신) (선경 0.4 · 외경 5 · 자유장 10)</t>
         </is>
       </c>
       <c r="E14" s="17" t="n">
-        <v>1590</v>
+        <v>1100</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="G14" s="17">
         <f>F14*E14</f>
@@ -1069,11 +1069,11 @@
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/4387963066</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="35" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/8501265889</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24.9" customHeight="1" s="15">
       <c r="A15" s="16" t="n">
         <v>13</v>
       </c>
@@ -1089,14 +1089,14 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>압축 스프링 SUS304 (C147 대신) (선경 0.4 · 외경 5 · 자유장 10)</t>
+          <t>M3 렌치볼트 스텐 (M3×8)</t>
         </is>
       </c>
       <c r="E15" s="17" t="n">
-        <v>1100</v>
+        <v>50</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G15" s="17">
         <f>F15*E15</f>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8501265889</t>
+          <t>https://www.coupang.com/vp/products/6455358137</t>
         </is>
       </c>
     </row>
@@ -1124,14 +1124,14 @@
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>M3 렌치볼트 스텐 (M3×8)</t>
+          <t>M3 렌치볼트 스텐 (M3×10)</t>
         </is>
       </c>
       <c r="E16" s="17" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G16" s="17">
         <f>F16*E16</f>
@@ -1159,14 +1159,14 @@
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>M3 렌치볼트 스텐 (M3×10)</t>
+          <t>M3 렌치볼트 스텐 (M3×12)</t>
         </is>
       </c>
       <c r="E17" s="17" t="n">
         <v>60</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="G17" s="17">
         <f>F17*E17</f>
@@ -1194,14 +1194,14 @@
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>M3 렌치볼트 스텐 (M3×12)</t>
+          <t>M3 렌치볼트 스텐 (M3×16)</t>
         </is>
       </c>
       <c r="E18" s="17" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="G18" s="17">
         <f>F18*E18</f>
@@ -1229,14 +1229,14 @@
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>M3 렌치볼트 스텐 (M3×16)</t>
+          <t>M3 렌치볼트 스텐 (M3×20)</t>
         </is>
       </c>
       <c r="E19" s="17" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G19" s="17">
         <f>F19*E19</f>
@@ -1264,14 +1264,14 @@
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>M3 렌치볼트 스텐 (M3×20)</t>
+          <t>M3 렌치볼트 스텐 (M3×25)</t>
         </is>
       </c>
       <c r="E20" s="17" t="n">
         <v>70</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G20" s="17">
         <f>F20*E20</f>
@@ -1299,14 +1299,14 @@
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>M3 렌치볼트 스텐 (M3×25)</t>
+          <t>M3 렌치볼트 스텐 (M3×50)</t>
         </is>
       </c>
       <c r="E21" s="17" t="n">
-        <v>70</v>
+        <v>170</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G21" s="17">
         <f>F21*E21</f>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>M3 렌치볼트 스텐 (M3×50)</t>
+          <t>M3 육각너트 스텐 (M3 (맞변 5.5))</t>
         </is>
       </c>
       <c r="E22" s="17" t="n">
-        <v>170</v>
+        <v>60</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G22" s="17">
         <f>F22*E22</f>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6455358137</t>
+          <t>https://www.coupang.com/vp/products/8532240860</t>
         </is>
       </c>
     </row>
@@ -1369,14 +1369,14 @@
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>M3 육각너트 스텐 (M3 (맞변 5.5))</t>
+          <t>M3 무두볼트 스텐 (오목끝) (M3×8)</t>
         </is>
       </c>
       <c r="E23" s="17" t="n">
         <v>60</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G23" s="17">
         <f>F23*E23</f>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8532240860</t>
+          <t>https://www.coupang.com/vp/products/7974822838</t>
         </is>
       </c>
     </row>
@@ -1404,14 +1404,14 @@
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>M3 무두볼트 스텐 (오목끝) (M3×8)</t>
+          <t>M3 평와셔 스텐 (바깥 8 × 두께 0.5)</t>
         </is>
       </c>
       <c r="E24" s="17" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G24" s="17">
         <f>F24*E24</f>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/7974822838</t>
+          <t>https://www.coupang.com/vp/products/7440529428</t>
         </is>
       </c>
     </row>
@@ -1439,14 +1439,14 @@
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>M3 평와셔 스텐 (바깥 8 × 두께 0.5)</t>
+          <t>M4 렌치볼트 스텐 (M4×16)</t>
         </is>
       </c>
       <c r="E25" s="17" t="n">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G25" s="17">
         <f>F25*E25</f>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/7440529428</t>
+          <t>https://www.coupang.com/vp/products/6455358137</t>
         </is>
       </c>
     </row>
@@ -1474,11 +1474,11 @@
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>M4 렌치볼트 스텐 (M4×16)</t>
+          <t>M4 렌치볼트 스텐 (M4×25)</t>
         </is>
       </c>
       <c r="E26" s="17" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>5</v>
@@ -1509,14 +1509,14 @@
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>M4 렌치볼트 스텐 (M4×25)</t>
+          <t>M4 렌치볼트 스텐 (M4×30)</t>
         </is>
       </c>
       <c r="E27" s="17" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="G27" s="17">
         <f>F27*E27</f>
@@ -1544,14 +1544,14 @@
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>M4 렌치볼트 스텐 (M4×30)</t>
+          <t>M4 렌치볼트 스텐 (M4×60)</t>
         </is>
       </c>
       <c r="E28" s="17" t="n">
-        <v>130</v>
+        <v>290</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="G28" s="17">
         <f>F28*E28</f>
@@ -1579,14 +1579,14 @@
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>M4 렌치볼트 스텐 (M4×60)</t>
+          <t>M4 육각너트 스텐 (M4 (맞변 7))</t>
         </is>
       </c>
       <c r="E29" s="17" t="n">
-        <v>290</v>
+        <v>60</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G29" s="17">
         <f>F29*E29</f>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6455358137</t>
+          <t>https://www.coupang.com/vp/products/8531939792</t>
         </is>
       </c>
     </row>
@@ -1614,14 +1614,14 @@
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>M4 육각너트 스텐 (M4 (맞변 7))</t>
+          <t>M5 렌치볼트 스텐 (M5×10)</t>
         </is>
       </c>
       <c r="E30" s="17" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G30" s="17">
         <f>F30*E30</f>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8531939792</t>
+          <t>https://www.coupang.com/vp/products/6455358137</t>
         </is>
       </c>
     </row>
@@ -1649,14 +1649,14 @@
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>M5 렌치볼트 스텐 (M5×10)</t>
+          <t>M5 렌치볼트 스텐 (M5×20)</t>
         </is>
       </c>
       <c r="E31" s="17" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G31" s="17">
         <f>F31*E31</f>
@@ -1684,14 +1684,14 @@
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>M5 렌치볼트 스텐 (M5×20)</t>
+          <t>M5 육각너트 스텐 (M5 (맞변 8))</t>
         </is>
       </c>
       <c r="E32" s="17" t="n">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G32" s="17">
         <f>F32*E32</f>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6455358137</t>
+          <t>https://www.coupang.com/vp/products/8531595719</t>
         </is>
       </c>
     </row>
@@ -1719,14 +1719,14 @@
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>M5 육각너트 스텐 (M5 (맞변 8))</t>
+          <t>M5 렌치볼트 스텐 (조정용) (M5×8)</t>
         </is>
       </c>
       <c r="E33" s="17" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G33" s="17">
         <f>F33*E33</f>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8531595719</t>
+          <t>https://www.coupang.com/vp/products/6455358137</t>
         </is>
       </c>
     </row>
@@ -1754,11 +1754,11 @@
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>M5 렌치볼트 스텐 (조정용) (M5×8)</t>
+          <t>M5 렌치볼트 스텐 (조정용) (M5×12)</t>
         </is>
       </c>
       <c r="E34" s="17" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F34" s="12" t="n">
         <v>3</v>
@@ -1789,11 +1789,11 @@
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>M5 렌치볼트 스텐 (조정용) (M5×12)</t>
+          <t>M5 평와셔 스텐 (바깥 12 × 두께 0.5)</t>
         </is>
       </c>
       <c r="E35" s="17" t="n">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="F35" s="12" t="n">
         <v>3</v>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="H35" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6455358137</t>
+          <t>https://www.coupang.com/vp/products/7440529428</t>
         </is>
       </c>
     </row>
@@ -1824,14 +1824,14 @@
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>M5 평와셔 스텐 (바깥 12 × 두께 0.5)</t>
+          <t>M5 렌치볼트 스텐 (M5×70)</t>
         </is>
       </c>
       <c r="E36" s="17" t="n">
-        <v>30</v>
+        <v>470</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G36" s="17">
         <f>F36*E36</f>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/7440529428</t>
+          <t>https://www.coupang.com/vp/products/6455358137</t>
         </is>
       </c>
     </row>
@@ -1859,11 +1859,11 @@
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>M5 렌치볼트 스텐 (M5×70)</t>
+          <t>M5 나일론 너트 스텐 (M5 (DIN985))</t>
         </is>
       </c>
       <c r="E37" s="17" t="n">
-        <v>470</v>
+        <v>80</v>
       </c>
       <c r="F37" s="12" t="n">
         <v>2</v>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="H37" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6455358137</t>
+          <t>https://www.coupang.com/vp/products/6280971320</t>
         </is>
       </c>
     </row>
@@ -1894,14 +1894,14 @@
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>M5 나일론 너트 스텐 (M5 (DIN985))</t>
+          <t>M6 렌치볼트 스텐 (M6×25)</t>
         </is>
       </c>
       <c r="E38" s="17" t="n">
-        <v>80</v>
+        <v>210</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G38" s="17">
         <f>F38*E38</f>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6280971320</t>
+          <t>https://www.coupang.com/vp/products/6455358137</t>
         </is>
       </c>
     </row>
@@ -1929,14 +1929,14 @@
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>M6 렌치볼트 스텐 (M6×25)</t>
+          <t>M6 육각너트 스텐 (M6 (맞변 10))</t>
         </is>
       </c>
       <c r="E39" s="17" t="n">
-        <v>210</v>
+        <v>60</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G39" s="17">
         <f>F39*E39</f>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6455358137</t>
+          <t>https://www.coupang.com/vp/products/7687671245</t>
         </is>
       </c>
     </row>
@@ -1964,14 +1964,14 @@
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>M6 육각너트 스텐 (M6 (맞변 10))</t>
+          <t>M6 나일론 너트 스텐 (M6 (DIN985))</t>
         </is>
       </c>
       <c r="E40" s="17" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G40" s="17">
         <f>F40*E40</f>
@@ -1979,11 +1979,11 @@
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/7687671245</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="24.9" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/6280971320</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="35" customHeight="1" s="15">
       <c r="A41" s="16" t="n">
         <v>39</v>
       </c>
@@ -1999,14 +1999,14 @@
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>M6 나일론 너트 스텐 (M6 (DIN985))</t>
+          <t>목재 나사 스텐 둥근머리 (4×16, 26개 봉)</t>
         </is>
       </c>
       <c r="E41" s="17" t="n">
-        <v>70</v>
+        <v>1150</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G41" s="17">
         <f>F41*E41</f>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="H41" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6280971320</t>
+          <t>https://www.coupang.com/vp/products/7760964029</t>
         </is>
       </c>
     </row>
@@ -2034,11 +2034,11 @@
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>목재 나사 스텐 둥근머리 (4×16, 26개 봉)</t>
+          <t>PLA 필라멘트 LeoPlas 2.85mm 1kg 검정 (2.85mm, 1kg)</t>
         </is>
       </c>
       <c r="E42" s="17" t="n">
-        <v>1150</v>
+        <v>41900</v>
       </c>
       <c r="F42" s="12" t="n">
         <v>2</v>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/7760964029</t>
+          <t>https://www.11st.co.kr/products/9216386785</t>
         </is>
       </c>
     </row>
@@ -2069,11 +2069,11 @@
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>PLA 필라멘트 2.85mm 1kg 검정 (2.85mm, 1kg)</t>
+          <t>PLA 필라멘트 LeoPlas 2.85mm 1kg 주황 (2.85mm, 1kg)</t>
         </is>
       </c>
       <c r="E43" s="17" t="n">
-        <v>35000</v>
+        <v>41900</v>
       </c>
       <c r="F43" s="12" t="n">
         <v>2</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=PLA 필라멘트 2.85mm 1kg</t>
+          <t>https://www.11st.co.kr/products/9216386785</t>
         </is>
       </c>
     </row>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>PLA 필라멘트 2.85mm 1kg 주황 (2.85mm, 1kg)</t>
+          <t>PLA 필라멘트 LeoPlas 2.85mm 1kg 파랑 (2.85mm, 1kg)</t>
         </is>
       </c>
       <c r="E44" s="17" t="n">
-        <v>35000</v>
+        <v>41900</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G44" s="17">
         <f>F44*E44</f>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=PLA 필라멘트 2.85mm 1kg</t>
+          <t>https://www.11st.co.kr/products/9216386785</t>
         </is>
       </c>
     </row>
@@ -2139,11 +2139,11 @@
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>PLA 필라멘트 2.85mm 1kg 파랑 (2.85mm, 1kg)</t>
+          <t>2액형 에폭시 접착제 (주사기형 25ml, 2개 묶음)</t>
         </is>
       </c>
       <c r="E45" s="17" t="n">
-        <v>35000</v>
+        <v>7650</v>
       </c>
       <c r="F45" s="12" t="n">
         <v>1</v>
@@ -2154,11 +2154,11 @@
       </c>
       <c r="H45" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=PLA 필라멘트 2.85mm 1kg</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="35" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/2725054</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="24.9" customHeight="1" s="15">
       <c r="A46" s="16" t="n">
         <v>44</v>
       </c>
@@ -2174,11 +2174,11 @@
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>2액형 에폭시 접착제 (주사기형 25ml, 2개 묶음)</t>
+          <t>순간접착제 (젤 타입 2개)</t>
         </is>
       </c>
       <c r="E46" s="17" t="n">
-        <v>7650</v>
+        <v>3000</v>
       </c>
       <c r="F46" s="12" t="n">
         <v>1</v>
@@ -2189,11 +2189,11 @@
       </c>
       <c r="H46" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/2725054</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="24.9" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/8643897709</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="35" customHeight="1" s="15">
       <c r="A47" s="16" t="n">
         <v>45</v>
       </c>
@@ -2209,11 +2209,11 @@
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>순간접착제 (젤 타입 2개)</t>
+          <t>자전거 브레이크 케이블 세트 (속선 2 + 아우터 + 끝 캡)</t>
         </is>
       </c>
       <c r="E47" s="17" t="n">
-        <v>3000</v>
+        <v>6900</v>
       </c>
       <c r="F47" s="12" t="n">
         <v>1</v>
@@ -2224,11 +2224,11 @@
       </c>
       <c r="H47" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8643897709</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="35" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/8305908512</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="24.9" customHeight="1" s="15">
       <c r="A48" s="16" t="n">
         <v>46</v>
       </c>
@@ -2244,11 +2244,11 @@
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>자전거 브레이크 케이블 세트 (속선 2 + 아우터 + 끝 캡)</t>
+          <t>MDF 판 (12T 300×1200 재단)</t>
         </is>
       </c>
       <c r="E48" s="17" t="n">
-        <v>6900</v>
+        <v>9600</v>
       </c>
       <c r="F48" s="12" t="n">
         <v>1</v>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="H48" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8305908512</t>
+          <t>https://www.coupang.com/vp/products/71452005</t>
         </is>
       </c>
     </row>
@@ -2279,11 +2279,11 @@
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>MDF 판 (12T 300×1200 재단)</t>
+          <t>투명 아크릴 3T 치수 재단 (250×321)</t>
         </is>
       </c>
       <c r="E49" s="17" t="n">
-        <v>9600</v>
+        <v>6000</v>
       </c>
       <c r="F49" s="12" t="n">
         <v>1</v>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="H49" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/71452005</t>
+          <t>https://www.11st.co.kr/products/4918717495</t>
         </is>
       </c>
     </row>
@@ -2314,14 +2314,14 @@
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>투명 아크릴 3T 치수 재단 (250×321)</t>
+          <t>투명 아크릴 3T 치수 재단 (200×321)</t>
         </is>
       </c>
       <c r="E50" s="17" t="n">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G50" s="17">
         <f>F50*E50</f>
@@ -2349,14 +2349,14 @@
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>투명 아크릴 3T 치수 재단 (200×321)</t>
+          <t>PTFE 그리스 (슈퍼루브) (85g)</t>
         </is>
       </c>
       <c r="E51" s="17" t="n">
-        <v>5000</v>
+        <v>9900</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G51" s="17">
         <f>F51*E51</f>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="H51" s="12" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/4918717495</t>
+          <t>https://www.coupang.com/vp/products/6071008034</t>
         </is>
       </c>
     </row>
@@ -2384,11 +2384,11 @@
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>PTFE 그리스 (슈퍼루브) (85g)</t>
+          <t>나사 고정제 록타이트 243 (10ml)</t>
         </is>
       </c>
       <c r="E52" s="17" t="n">
-        <v>9900</v>
+        <v>8580</v>
       </c>
       <c r="F52" s="12" t="n">
         <v>1</v>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="H52" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6071008034</t>
+          <t>https://www.11st.co.kr/products/7426834008</t>
         </is>
       </c>
     </row>
@@ -2419,11 +2419,11 @@
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>나사 고정제 록타이트 243 (10ml)</t>
+          <t>열수축 튜브 세트 (1~14mm 164개)</t>
         </is>
       </c>
       <c r="E53" s="17" t="n">
-        <v>8580</v>
+        <v>750</v>
       </c>
       <c r="F53" s="12" t="n">
         <v>1</v>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="H53" s="12" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/7426834008</t>
+          <t>https://www.coupang.com/vp/products/9183828751</t>
         </is>
       </c>
     </row>
@@ -2454,11 +2454,11 @@
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>열수축 튜브 세트 (1~14mm 164개)</t>
+          <t>케이블 타이 (100개, 흑색)</t>
         </is>
       </c>
       <c r="E54" s="17" t="n">
-        <v>750</v>
+        <v>770</v>
       </c>
       <c r="F54" s="12" t="n">
         <v>1</v>
@@ -2469,11 +2469,11 @@
       </c>
       <c r="H54" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9183828751</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="24.9" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/8850608631</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="35" customHeight="1" s="15">
       <c r="A55" s="16" t="n">
         <v>53</v>
       </c>
@@ -2489,14 +2489,14 @@
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>케이블 타이 (100개, 흑색)</t>
+          <t>신호선 0.3SQ (약 22AWG) 10색 (10색 × 1m 세트)</t>
         </is>
       </c>
       <c r="E55" s="17" t="n">
-        <v>770</v>
+        <v>1500</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G55" s="17">
         <f>F55*E55</f>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="H55" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8850608631</t>
+          <t>https://www.coupang.com/vp/products/9183828539</t>
         </is>
       </c>
     </row>
@@ -2524,14 +2524,14 @@
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>신호선 0.3SQ (약 22AWG) 10색 (10색 × 1m 세트)</t>
+          <t>탁상 바이스 ITL 80mm (주물, 360도 회전, 책상 모서리 클램프 (ITL-0124))</t>
         </is>
       </c>
       <c r="E56" s="17" t="n">
-        <v>1500</v>
+        <v>20900</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G56" s="17">
         <f>F56*E56</f>
@@ -2539,11 +2539,11 @@
       </c>
       <c r="H56" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9183828539</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="35" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/9035202709</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="24.9" customHeight="1" s="15">
       <c r="A57" s="16" t="n">
         <v>55</v>
       </c>
@@ -2559,11 +2559,11 @@
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>디지털 캘리퍼스 (150mm, 분해능 0.01mm)</t>
+          <t>철공용 평줄 중목 (250mm)</t>
         </is>
       </c>
       <c r="E57" s="17" t="n">
-        <v>20000</v>
+        <v>5800</v>
       </c>
       <c r="F57" s="12" t="n">
         <v>1</v>
@@ -2574,11 +2574,11 @@
       </c>
       <c r="H57" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=디지털 캘리퍼스 150mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="35" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/8997744652</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="24.9" customHeight="1" s="15">
       <c r="A58" s="16" t="n">
         <v>56</v>
       </c>
@@ -2594,11 +2594,11 @@
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>탁상 바이스 (조 폭 75~100mm, 책상에 클램프 고정)</t>
+          <t>철공용 평줄 세목 (200mm)</t>
         </is>
       </c>
       <c r="E58" s="17" t="n">
-        <v>20000</v>
+        <v>4600</v>
       </c>
       <c r="F58" s="12" t="n">
         <v>1</v>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="H58" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=탁상 바이스</t>
+          <t>https://www.coupang.com/vp/products/8997744821</t>
         </is>
       </c>
     </row>
@@ -2629,11 +2629,11 @@
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>철공용 평줄 중목 (250mm)</t>
+          <t>플랩 디스크 100mm #80 (10개 봉)</t>
         </is>
       </c>
       <c r="E59" s="17" t="n">
-        <v>5800</v>
+        <v>7500</v>
       </c>
       <c r="F59" s="12" t="n">
         <v>1</v>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="H59" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8997744652</t>
+          <t>https://www.coupang.com/vp/products/9416862249</t>
         </is>
       </c>
     </row>
@@ -2664,11 +2664,11 @@
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>철공용 평줄 세목 (200mm)</t>
+          <t>절단석 105mm 두께 1mm (5개 봉)</t>
         </is>
       </c>
       <c r="E60" s="17" t="n">
-        <v>4600</v>
+        <v>4000</v>
       </c>
       <c r="F60" s="12" t="n">
         <v>1</v>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="H60" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8997744821</t>
+          <t>https://www.coupang.com/vp/products/9375758010</t>
         </is>
       </c>
     </row>
@@ -2699,11 +2699,11 @@
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>플랩 디스크 100mm #80 (10개 봉)</t>
+          <t>보안경 (측면 보호) (투명)</t>
         </is>
       </c>
       <c r="E61" s="17" t="n">
-        <v>7500</v>
+        <v>6290</v>
       </c>
       <c r="F61" s="12" t="n">
         <v>1</v>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="H61" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9416862249</t>
+          <t>https://www.coupang.com/vp/products/8800840444</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>절단석 105mm 두께 1mm (5개 봉)</t>
+          <t>NBR 코팅 장갑 가드맨 (L, 3켤레)</t>
         </is>
       </c>
       <c r="E62" s="17" t="n">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="H62" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9375758010</t>
+          <t>https://www.coupang.com/vp/products/8531708909</t>
         </is>
       </c>
     </row>
@@ -2769,11 +2769,11 @@
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>보안경 (측면 보호) (투명)</t>
+          <t>코발트 드릴 날 2.5mm (육각 생크, 3개)</t>
         </is>
       </c>
       <c r="E63" s="17" t="n">
-        <v>6290</v>
+        <v>3450</v>
       </c>
       <c r="F63" s="12" t="n">
         <v>1</v>
@@ -2784,11 +2784,11 @@
       </c>
       <c r="H63" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8800840444</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="24.9" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/1479107481</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="35" customHeight="1" s="15">
       <c r="A64" s="16" t="n">
         <v>62</v>
       </c>
@@ -2804,11 +2804,11 @@
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>NBR 코팅 장갑 (L)</t>
+          <t>C클램프 4인치 (최대 벌림 105mm, 2개 묶음)</t>
         </is>
       </c>
       <c r="E64" s="17" t="n">
-        <v>3000</v>
+        <v>10490</v>
       </c>
       <c r="F64" s="12" t="n">
         <v>1</v>
@@ -2819,11 +2819,11 @@
       </c>
       <c r="H64" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=NBR 코팅장갑</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="24.9" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/8261073812</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="35" customHeight="1" s="15">
       <c r="A65" s="16" t="n">
         <v>63</v>
       </c>
@@ -2839,11 +2839,11 @@
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>HSS 드릴 날 2.5mm (1개)</t>
+          <t>아두이노 레오나르도 R3 + USB 케이블 (ATmega32u4)</t>
         </is>
       </c>
       <c r="E65" s="17" t="n">
-        <v>2000</v>
+        <v>9200</v>
       </c>
       <c r="F65" s="12" t="n">
         <v>1</v>
@@ -2854,11 +2854,11 @@
       </c>
       <c r="H65" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=HSS 드릴날 2.5mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="35" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/1119152790</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="24.9" customHeight="1" s="15">
       <c r="A66" s="16" t="n">
         <v>64</v>
       </c>
@@ -2874,14 +2874,14 @@
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>C클램프 4인치 (최대 벌림 105mm, 2개 묶음)</t>
+          <t>홀센서 A3144 (3핀)</t>
         </is>
       </c>
       <c r="E66" s="17" t="n">
-        <v>10490</v>
+        <v>90</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G66" s="17">
         <f>F66*E66</f>
@@ -2889,11 +2889,11 @@
       </c>
       <c r="H66" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8261073812</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="35" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/8520223332</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="24.9" customHeight="1" s="15">
       <c r="A67" s="16" t="n">
         <v>65</v>
       </c>
@@ -2909,11 +2909,11 @@
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>아두이노 레오나르도 R3 + USB 케이블 (ATmega32u4)</t>
+          <t>네오디뮴 자석 (Ø6×3, 40개)</t>
         </is>
       </c>
       <c r="E67" s="17" t="n">
-        <v>9200</v>
+        <v>11300</v>
       </c>
       <c r="F67" s="12" t="n">
         <v>1</v>
@@ -2924,11 +2924,11 @@
       </c>
       <c r="H67" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/1119152790</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="24.9" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/7119515778</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="35" customHeight="1" s="15">
       <c r="A68" s="16" t="n">
         <v>66</v>
       </c>
@@ -2944,14 +2944,14 @@
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>홀센서 A3144 (3핀)</t>
+          <t>가변저항 10K WH148 톱니 축 (16mm, 축 15mm, 부싱 M7, 3핀)</t>
         </is>
       </c>
       <c r="E68" s="17" t="n">
-        <v>90</v>
+        <v>240</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G68" s="17">
         <f>F68*E68</f>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="H68" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8520223332</t>
+          <t>https://www.coupang.com/vp/products/8718871111</t>
         </is>
       </c>
     </row>
@@ -2979,14 +2979,14 @@
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>네오디뮴 자석 (Ø6×3, 40개)</t>
+          <t>마이크로스위치 KW-11-3Z (레버형)</t>
         </is>
       </c>
       <c r="E69" s="17" t="n">
-        <v>11300</v>
+        <v>400</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G69" s="17">
         <f>F69*E69</f>
@@ -2994,11 +2994,11 @@
       </c>
       <c r="H69" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/7119515778</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="35" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/9167678186</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="24.9" customHeight="1" s="15">
       <c r="A70" s="16" t="n">
         <v>68</v>
       </c>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>가변저항 10K WH148 톱니 축 (16mm, 축 15mm, 부싱 M7, 3핀)</t>
+          <t>점퍼 케이블 F-M (40P 40cm)</t>
         </is>
       </c>
       <c r="E70" s="17" t="n">
-        <v>240</v>
+        <v>1300</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G70" s="17">
         <f>F70*E70</f>
@@ -3029,11 +3029,11 @@
       </c>
       <c r="H70" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8718871111</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="24.9" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/9183828363</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="35" customHeight="1" s="15">
       <c r="A71" s="16" t="n">
         <v>69</v>
       </c>
@@ -3049,14 +3049,14 @@
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>마이크로스위치 KW-11-3Z (레버형)</t>
+          <t>만능기판 양면 2.54 (28×43홀 (약 71×109mm))</t>
         </is>
       </c>
       <c r="E71" s="17" t="n">
-        <v>400</v>
+        <v>2700</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G71" s="17">
         <f>F71*E71</f>
@@ -3064,11 +3064,11 @@
       </c>
       <c r="H71" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9167678186</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="24.9" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/9181560693</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="35" customHeight="1" s="15">
       <c r="A72" s="16" t="n">
         <v>70</v>
       </c>
@@ -3084,11 +3084,11 @@
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>점퍼 케이블 F-M (40P 40cm)</t>
+          <t>자동차 릴레이 12V 40A + 소켓 (4핀, 배선된 소켓)</t>
         </is>
       </c>
       <c r="E72" s="17" t="n">
-        <v>1300</v>
+        <v>3100</v>
       </c>
       <c r="F72" s="12" t="n">
         <v>1</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="H72" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9183828363</t>
+          <t>https://www.coupang.com/vp/products/6667848502</t>
         </is>
       </c>
     </row>
@@ -3119,11 +3119,11 @@
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>만능기판 양면 2.54 (28×43홀 (약 71×109mm))</t>
+          <t>블레이드 퓨즈 + 인라인 홀더 세트 (15A 포함, 홀더 4 + 퓨즈 12)</t>
         </is>
       </c>
       <c r="E73" s="17" t="n">
-        <v>2700</v>
+        <v>8900</v>
       </c>
       <c r="F73" s="12" t="n">
         <v>1</v>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="H73" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9181560693</t>
+          <t>https://www.coupang.com/vp/products/9663070188</t>
         </is>
       </c>
     </row>
@@ -3154,11 +3154,11 @@
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>자동차 릴레이 12V 40A + 소켓 (4핀, 배선된 소켓)</t>
+          <t>비상정지 스위치 22mm + 1구 박스 (LAS0-K-11TSA, 1a1b)</t>
         </is>
       </c>
       <c r="E74" s="17" t="n">
-        <v>3100</v>
+        <v>18300</v>
       </c>
       <c r="F74" s="12" t="n">
         <v>1</v>
@@ -3169,11 +3169,11 @@
       </c>
       <c r="H74" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6667848502</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="35" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/9169916764</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="24.9" customHeight="1" s="15">
       <c r="A75" s="16" t="n">
         <v>73</v>
       </c>
@@ -3189,11 +3189,11 @@
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>블레이드 퓨즈 + 인라인 홀더 세트 (15A 포함, 홀더 4 + 퓨즈 12)</t>
+          <t>5V 릴레이 모듈 1채널 KY-019 (1채널)</t>
         </is>
       </c>
       <c r="E75" s="17" t="n">
-        <v>8900</v>
+        <v>550</v>
       </c>
       <c r="F75" s="12" t="n">
         <v>1</v>
@@ -3204,11 +3204,11 @@
       </c>
       <c r="H75" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9663070188</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="35" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/9162331915</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="24.9" customHeight="1" s="15">
       <c r="A76" s="16" t="n">
         <v>74</v>
       </c>
@@ -3224,11 +3224,11 @@
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>비상정지 스위치 22mm + 1구 박스 (LAS0-K-11TSA, 1a1b)</t>
+          <t>다이오드 1N4007 (10개)</t>
         </is>
       </c>
       <c r="E76" s="17" t="n">
-        <v>18300</v>
+        <v>690</v>
       </c>
       <c r="F76" s="12" t="n">
         <v>1</v>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="H76" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9169916764</t>
+          <t>https://www.coupang.com/vp/products/9705767581</t>
         </is>
       </c>
     </row>
@@ -3259,11 +3259,11 @@
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>5V 릴레이 모듈 1채널 KY-019 (1채널)</t>
+          <t>저항 1/4W 10kΩ (10개)</t>
         </is>
       </c>
       <c r="E77" s="17" t="n">
-        <v>550</v>
+        <v>80</v>
       </c>
       <c r="F77" s="12" t="n">
         <v>1</v>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="H77" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9162331915</t>
+          <t>https://www.coupang.com/vp/products/9701925630</t>
         </is>
       </c>
     </row>
@@ -3294,11 +3294,11 @@
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>다이오드 1N4007 (10개)</t>
+          <t>저항 1/4W 4.7kΩ (10개)</t>
         </is>
       </c>
       <c r="E78" s="17" t="n">
-        <v>690</v>
+        <v>80</v>
       </c>
       <c r="F78" s="12" t="n">
         <v>1</v>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="H78" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9705767581</t>
+          <t>https://www.coupang.com/vp/products/9701925630</t>
         </is>
       </c>
     </row>
@@ -3329,14 +3329,14 @@
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>저항 1/4W 10kΩ (10개)</t>
+          <t>실리콘 전선 16AWG 빨강·검정 (1m 세트)</t>
         </is>
       </c>
       <c r="E79" s="17" t="n">
-        <v>80</v>
+        <v>1310</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G79" s="17">
         <f>F79*E79</f>
@@ -3344,11 +3344,11 @@
       </c>
       <c r="H79" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9701925630</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="24.9" customHeight="1" s="15">
+          <t>https://www.coupang.com/vp/products/7225302003</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="35" customHeight="1" s="15">
       <c r="A80" s="16" t="n">
         <v>78</v>
       </c>
@@ -3364,11 +3364,11 @@
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>저항 1/4W 4.7kΩ (10개)</t>
+          <t>절연 암 평형 단자 250 (6.3mm) (10개 봉)</t>
         </is>
       </c>
       <c r="E80" s="17" t="n">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="F80" s="12" t="n">
         <v>1</v>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="H80" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9701925630</t>
+          <t>https://www.coupang.com/vp/products/9181548711</t>
         </is>
       </c>
     </row>
@@ -3399,14 +3399,14 @@
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>실리콘 전선 16AWG 빨강·검정 (1m 세트)</t>
+          <t>배송비 (판매처별 합계)</t>
         </is>
       </c>
       <c r="E81" s="17" t="n">
-        <v>1310</v>
+        <v>51800</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G81" s="17">
         <f>F81*E81</f>
@@ -3414,100 +3414,32 @@
       </c>
       <c r="H81" s="12" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/7225302003</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="35" customHeight="1" s="15">
-      <c r="A82" s="16" t="n">
-        <v>80</v>
-      </c>
-      <c r="B82" s="12" t="inlineStr">
-        <is>
-          <t>RPM</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="inlineStr">
-        <is>
-          <t>홍경표, 장수빈</t>
-        </is>
-      </c>
-      <c r="D82" s="12" t="inlineStr">
-        <is>
-          <t>절연 암 평형 단자 250 (6.3mm) (10개 봉)</t>
-        </is>
-      </c>
-      <c r="E82" s="17" t="n">
-        <v>800</v>
-      </c>
-      <c r="F82" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G82" s="17">
-        <f>F82*E82</f>
-        <v/>
-      </c>
-      <c r="H82" s="12" t="inlineStr">
-        <is>
-          <t>https://www.coupang.com/vp/products/9181548711</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="24.9" customHeight="1" s="15">
-      <c r="A83" s="16" t="n">
-        <v>81</v>
-      </c>
-      <c r="B83" s="12" t="inlineStr">
-        <is>
-          <t>RPM</t>
-        </is>
-      </c>
-      <c r="C83" s="12" t="inlineStr">
-        <is>
-          <t>홍경표, 장수빈</t>
-        </is>
-      </c>
-      <c r="D83" s="12" t="inlineStr">
-        <is>
-          <t>배송비 (판매처별 합계)</t>
-        </is>
-      </c>
-      <c r="E83" s="17" t="n">
-        <v>57800</v>
-      </c>
-      <c r="F83" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="17">
-        <f>F83*E83</f>
-        <v/>
-      </c>
-      <c r="H83" s="12" t="inlineStr">
-        <is>
           <t>판매처별 배송비 합계</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="9" t="n"/>
-      <c r="B84" s="6" t="n"/>
-      <c r="C84" s="6" t="n"/>
-      <c r="D84" s="6" t="n"/>
-      <c r="E84" s="18" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="9" t="n"/>
+      <c r="B82" s="6" t="n"/>
+      <c r="C82" s="6" t="n"/>
+      <c r="D82" s="6" t="n"/>
+      <c r="E82" s="18" t="inlineStr">
         <is>
           <t>소계</t>
         </is>
       </c>
-      <c r="F84" s="19">
-        <f>SUM(F3:F83)</f>
-        <v/>
-      </c>
-      <c r="G84" s="20">
-        <f>SUM(G3:G83)</f>
-        <v/>
-      </c>
-      <c r="H84" s="6" t="n"/>
-    </row>
+      <c r="F82" s="19">
+        <f>SUM(F3:F81)</f>
+        <v/>
+      </c>
+      <c r="G82" s="20">
+        <f>SUM(G3:G81)</f>
+        <v/>
+      </c>
+      <c r="H82" s="6" t="n"/>
+    </row>
+    <row r="83" s="15"/>
+    <row r="84" s="15"/>
     <row r="85" s="15"/>
     <row r="86" s="15"/>
     <row r="87" s="15"/>
@@ -3525,8 +3457,6 @@
     <row r="99" s="15"/>
     <row r="100" s="15"/>
     <row r="101" s="15"/>
-    <row r="102" s="15"/>
-    <row r="103" s="15"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
@@ -3610,8 +3540,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId80"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
